--- a/Study.xlsx
+++ b/Study.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\DH_Main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82842E3F-E001-4748-9AB2-631EB56014AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CA801BA-46DD-486D-ABF2-3D66AE3FA68D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="267">
   <si>
     <t>Path</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -907,6 +907,12 @@
   </si>
   <si>
     <t>Introduction to PQC</t>
+  </si>
+  <si>
+    <t>Linux Kernel Attack Surfaces</t>
+  </si>
+  <si>
+    <t>Linux Kernel - Information Leak</t>
   </si>
 </sst>
 </file>
@@ -1463,6 +1469,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1475,12 +1484,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1508,6 +1517,18 @@
     <xf numFmtId="0" fontId="3" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1517,53 +1538,38 @@
     <xf numFmtId="0" fontId="3" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1880,14 +1886,14 @@
       <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="75" t="s">
+      <c r="C1" s="76" t="s">
         <v>220</v>
       </c>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75" t="s">
+      <c r="D1" s="76"/>
+      <c r="E1" s="76" t="s">
         <v>224</v>
       </c>
-      <c r="F1" s="75"/>
+      <c r="F1" s="76"/>
       <c r="G1" s="3" t="s">
         <v>221</v>
       </c>
@@ -1902,13 +1908,13 @@
       <c r="B2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="72">
+      <c r="C2" s="73">
         <v>0</v>
       </c>
       <c r="D2" s="5">
         <v>0</v>
       </c>
-      <c r="E2" s="72" t="s">
+      <c r="E2" s="73" t="s">
         <v>223</v>
       </c>
       <c r="F2" s="5" t="s">
@@ -1922,11 +1928,11 @@
       <c r="B3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="72"/>
+      <c r="C3" s="73"/>
       <c r="D3" s="5">
         <v>0</v>
       </c>
-      <c r="E3" s="72"/>
+      <c r="E3" s="73"/>
       <c r="F3" s="5" t="s">
         <v>223</v>
       </c>
@@ -1938,11 +1944,11 @@
       <c r="B4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="72"/>
+      <c r="C4" s="73"/>
       <c r="D4" s="5">
         <v>0</v>
       </c>
-      <c r="E4" s="72"/>
+      <c r="E4" s="73"/>
       <c r="F4" s="5" t="s">
         <v>223</v>
       </c>
@@ -1954,11 +1960,11 @@
       <c r="B5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="72"/>
+      <c r="C5" s="73"/>
       <c r="D5" s="5">
         <v>0</v>
       </c>
-      <c r="E5" s="72"/>
+      <c r="E5" s="73"/>
       <c r="F5" s="5" t="s">
         <v>223</v>
       </c>
@@ -1970,11 +1976,11 @@
       <c r="B6" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="72"/>
+      <c r="C6" s="73"/>
       <c r="D6" s="5">
         <v>0</v>
       </c>
-      <c r="E6" s="72"/>
+      <c r="E6" s="73"/>
       <c r="F6" s="5" t="s">
         <v>223</v>
       </c>
@@ -1986,11 +1992,11 @@
       <c r="B7" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="72"/>
+      <c r="C7" s="73"/>
       <c r="D7" s="5">
         <v>0</v>
       </c>
-      <c r="E7" s="72"/>
+      <c r="E7" s="73"/>
       <c r="F7" s="5" t="s">
         <v>223</v>
       </c>
@@ -2002,11 +2008,11 @@
       <c r="B8" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="72"/>
+      <c r="C8" s="73"/>
       <c r="D8" s="5">
         <v>0</v>
       </c>
-      <c r="E8" s="72"/>
+      <c r="E8" s="73"/>
       <c r="F8" s="5" t="s">
         <v>223</v>
       </c>
@@ -2020,13 +2026,13 @@
       <c r="B9" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="72">
+      <c r="C9" s="73">
         <v>0</v>
       </c>
       <c r="D9" s="5">
         <v>0</v>
       </c>
-      <c r="E9" s="72" t="s">
+      <c r="E9" s="73" t="s">
         <v>223</v>
       </c>
       <c r="F9" s="5" t="s">
@@ -2040,11 +2046,11 @@
       <c r="B10" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="72"/>
+      <c r="C10" s="73"/>
       <c r="D10" s="5">
         <v>0</v>
       </c>
-      <c r="E10" s="72"/>
+      <c r="E10" s="73"/>
       <c r="F10" s="5" t="s">
         <v>223</v>
       </c>
@@ -2056,11 +2062,11 @@
       <c r="B11" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="72"/>
+      <c r="C11" s="73"/>
       <c r="D11" s="5">
         <v>0</v>
       </c>
-      <c r="E11" s="72"/>
+      <c r="E11" s="73"/>
       <c r="F11" s="5" t="s">
         <v>223</v>
       </c>
@@ -2072,11 +2078,11 @@
       <c r="B12" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="72"/>
+      <c r="C12" s="73"/>
       <c r="D12" s="5">
         <v>0</v>
       </c>
-      <c r="E12" s="72"/>
+      <c r="E12" s="73"/>
       <c r="F12" s="5" t="s">
         <v>223</v>
       </c>
@@ -2088,11 +2094,11 @@
       <c r="B13" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="72"/>
+      <c r="C13" s="73"/>
       <c r="D13" s="5">
         <v>0</v>
       </c>
-      <c r="E13" s="72"/>
+      <c r="E13" s="73"/>
       <c r="F13" s="5" t="s">
         <v>223</v>
       </c>
@@ -2104,11 +2110,11 @@
       <c r="B14" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="72"/>
+      <c r="C14" s="73"/>
       <c r="D14" s="5">
         <v>0</v>
       </c>
-      <c r="E14" s="72"/>
+      <c r="E14" s="73"/>
       <c r="F14" s="5" t="s">
         <v>223</v>
       </c>
@@ -2120,11 +2126,11 @@
       <c r="B15" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="72"/>
+      <c r="C15" s="73"/>
       <c r="D15" s="5">
         <v>0</v>
       </c>
-      <c r="E15" s="72"/>
+      <c r="E15" s="73"/>
       <c r="F15" s="5" t="s">
         <v>223</v>
       </c>
@@ -2136,11 +2142,11 @@
       <c r="B16" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="72"/>
+      <c r="C16" s="73"/>
       <c r="D16" s="5">
         <v>0</v>
       </c>
-      <c r="E16" s="72"/>
+      <c r="E16" s="73"/>
       <c r="F16" s="5" t="s">
         <v>223</v>
       </c>
@@ -2154,13 +2160,13 @@
       <c r="B17" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C17" s="72">
+      <c r="C17" s="73">
         <v>0</v>
       </c>
       <c r="D17" s="5">
         <v>0</v>
       </c>
-      <c r="E17" s="72" t="s">
+      <c r="E17" s="73" t="s">
         <v>223</v>
       </c>
       <c r="F17" s="5" t="s">
@@ -2174,11 +2180,11 @@
       <c r="B18" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="72"/>
+      <c r="C18" s="73"/>
       <c r="D18" s="5">
         <v>0</v>
       </c>
-      <c r="E18" s="72"/>
+      <c r="E18" s="73"/>
       <c r="F18" s="5" t="s">
         <v>223</v>
       </c>
@@ -2190,11 +2196,11 @@
       <c r="B19" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="72"/>
+      <c r="C19" s="73"/>
       <c r="D19" s="5">
         <v>0</v>
       </c>
-      <c r="E19" s="72"/>
+      <c r="E19" s="73"/>
       <c r="F19" s="54" t="s">
         <v>223</v>
       </c>
@@ -2206,11 +2212,11 @@
       <c r="B20" t="s">
         <v>253</v>
       </c>
-      <c r="C20" s="72"/>
+      <c r="C20" s="73"/>
       <c r="D20" s="2">
         <v>0</v>
       </c>
-      <c r="E20" s="73"/>
+      <c r="E20" s="75"/>
       <c r="F20" s="56" t="s">
         <v>223</v>
       </c>
@@ -2224,13 +2230,13 @@
       <c r="B21" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C21" s="72">
+      <c r="C21" s="73">
         <v>0</v>
       </c>
       <c r="D21" s="5">
         <v>0</v>
       </c>
-      <c r="E21" s="73" t="s">
+      <c r="E21" s="75" t="s">
         <v>223</v>
       </c>
       <c r="F21" s="38" t="s">
@@ -2244,11 +2250,11 @@
       <c r="B22" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C22" s="72"/>
+      <c r="C22" s="73"/>
       <c r="D22" s="5">
         <v>0</v>
       </c>
-      <c r="E22" s="73"/>
+      <c r="E22" s="75"/>
       <c r="F22" s="38" t="s">
         <v>223</v>
       </c>
@@ -2260,11 +2266,11 @@
       <c r="B23" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C23" s="72"/>
+      <c r="C23" s="73"/>
       <c r="D23" s="5">
         <v>0</v>
       </c>
-      <c r="E23" s="72"/>
+      <c r="E23" s="73"/>
       <c r="F23" s="55" t="s">
         <v>223</v>
       </c>
@@ -2276,11 +2282,11 @@
       <c r="B24" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C24" s="72"/>
+      <c r="C24" s="73"/>
       <c r="D24" s="5">
         <v>0</v>
       </c>
-      <c r="E24" s="72"/>
+      <c r="E24" s="73"/>
       <c r="F24" s="5" t="s">
         <v>225</v>
       </c>
@@ -2292,11 +2298,11 @@
       <c r="B25" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C25" s="72"/>
+      <c r="C25" s="73"/>
       <c r="D25" s="5">
         <v>0</v>
       </c>
-      <c r="E25" s="72"/>
+      <c r="E25" s="73"/>
       <c r="F25" s="5" t="s">
         <v>226</v>
       </c>
@@ -2310,13 +2316,13 @@
       <c r="B26" s="7" t="s">
         <v>249</v>
       </c>
-      <c r="C26" s="72">
+      <c r="C26" s="73">
         <v>0</v>
       </c>
       <c r="D26" s="5">
         <v>0</v>
       </c>
-      <c r="E26" s="72" t="s">
+      <c r="E26" s="73" t="s">
         <v>223</v>
       </c>
       <c r="F26" s="5" t="s">
@@ -2330,11 +2336,11 @@
       <c r="B27" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="C27" s="72"/>
+      <c r="C27" s="73"/>
       <c r="D27" s="5">
         <v>0</v>
       </c>
-      <c r="E27" s="72"/>
+      <c r="E27" s="73"/>
       <c r="F27" s="5" t="s">
         <v>225</v>
       </c>
@@ -2346,11 +2352,11 @@
       <c r="B28" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="72"/>
+      <c r="C28" s="73"/>
       <c r="D28" s="5">
         <v>0</v>
       </c>
-      <c r="E28" s="72"/>
+      <c r="E28" s="73"/>
       <c r="F28" s="5" t="s">
         <v>225</v>
       </c>
@@ -2362,11 +2368,11 @@
       <c r="B29" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C29" s="72"/>
+      <c r="C29" s="73"/>
       <c r="D29" s="5">
         <v>0</v>
       </c>
-      <c r="E29" s="72"/>
+      <c r="E29" s="73"/>
       <c r="F29" s="5" t="s">
         <v>225</v>
       </c>
@@ -2378,11 +2384,11 @@
       <c r="B30" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="C30" s="72"/>
+      <c r="C30" s="73"/>
       <c r="D30" s="5">
         <v>0</v>
       </c>
-      <c r="E30" s="72"/>
+      <c r="E30" s="73"/>
       <c r="F30" s="5" t="s">
         <v>223</v>
       </c>
@@ -2394,11 +2400,11 @@
       <c r="B31" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C31" s="72"/>
+      <c r="C31" s="73"/>
       <c r="D31" s="5">
         <v>0</v>
       </c>
-      <c r="E31" s="72"/>
+      <c r="E31" s="73"/>
       <c r="F31" s="5" t="s">
         <v>225</v>
       </c>
@@ -2410,11 +2416,11 @@
       <c r="B32" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C32" s="72"/>
+      <c r="C32" s="73"/>
       <c r="D32" s="5">
         <v>0</v>
       </c>
-      <c r="E32" s="72"/>
+      <c r="E32" s="73"/>
       <c r="F32" s="5" t="s">
         <v>225</v>
       </c>
@@ -2426,11 +2432,11 @@
       <c r="B33" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="C33" s="72"/>
+      <c r="C33" s="73"/>
       <c r="D33" s="5">
         <v>0</v>
       </c>
-      <c r="E33" s="72"/>
+      <c r="E33" s="73"/>
       <c r="F33" s="5" t="s">
         <v>226</v>
       </c>
@@ -2444,13 +2450,13 @@
       <c r="B34" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="C34" s="72">
+      <c r="C34" s="73">
         <v>1</v>
       </c>
       <c r="D34" s="5">
         <v>1</v>
       </c>
-      <c r="E34" s="72" t="s">
+      <c r="E34" s="73" t="s">
         <v>223</v>
       </c>
       <c r="F34" s="5" t="s">
@@ -2464,11 +2470,11 @@
       <c r="B35" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C35" s="72"/>
+      <c r="C35" s="73"/>
       <c r="D35" s="5">
         <v>1</v>
       </c>
-      <c r="E35" s="72"/>
+      <c r="E35" s="73"/>
       <c r="F35" s="5" t="s">
         <v>223</v>
       </c>
@@ -2480,11 +2486,11 @@
       <c r="B36" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="C36" s="72"/>
+      <c r="C36" s="73"/>
       <c r="D36" s="5">
         <v>1</v>
       </c>
-      <c r="E36" s="72"/>
+      <c r="E36" s="73"/>
       <c r="F36" s="5" t="s">
         <v>223</v>
       </c>
@@ -2496,11 +2502,11 @@
       <c r="B37" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="C37" s="72"/>
+      <c r="C37" s="73"/>
       <c r="D37" s="23">
         <v>1</v>
       </c>
-      <c r="E37" s="72"/>
+      <c r="E37" s="73"/>
       <c r="F37" s="23" t="s">
         <v>223</v>
       </c>
@@ -2516,7 +2522,7 @@
       <c r="D38" s="23">
         <v>1</v>
       </c>
-      <c r="E38" s="72"/>
+      <c r="E38" s="73"/>
       <c r="F38" s="23" t="s">
         <v>223</v>
       </c>
@@ -2532,7 +2538,7 @@
       <c r="D39" s="23">
         <v>1</v>
       </c>
-      <c r="E39" s="72"/>
+      <c r="E39" s="73"/>
       <c r="F39" s="23" t="s">
         <v>223</v>
       </c>
@@ -2548,7 +2554,7 @@
       <c r="D40" s="5">
         <v>1</v>
       </c>
-      <c r="E40" s="72"/>
+      <c r="E40" s="73"/>
       <c r="F40" s="5" t="s">
         <v>223</v>
       </c>
@@ -2556,19 +2562,19 @@
       <c r="H40" s="20"/>
     </row>
     <row r="41" spans="1:8">
-      <c r="A41" s="84" t="s">
+      <c r="A41" s="89" t="s">
         <v>47</v>
       </c>
       <c r="B41" s="25" t="s">
         <v>239</v>
       </c>
-      <c r="C41" s="72">
+      <c r="C41" s="73">
         <v>1</v>
       </c>
       <c r="D41" s="5">
         <v>0</v>
       </c>
-      <c r="E41" s="72" t="s">
+      <c r="E41" s="73" t="s">
         <v>225</v>
       </c>
       <c r="F41" s="5" t="s">
@@ -2578,15 +2584,15 @@
       <c r="H41" s="30"/>
     </row>
     <row r="42" spans="1:8">
-      <c r="A42" s="84"/>
+      <c r="A42" s="89"/>
       <c r="B42" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C42" s="72"/>
+      <c r="C42" s="73"/>
       <c r="D42" s="5">
         <v>1</v>
       </c>
-      <c r="E42" s="72"/>
+      <c r="E42" s="73"/>
       <c r="F42" s="5" t="s">
         <v>225</v>
       </c>
@@ -2594,15 +2600,15 @@
       <c r="H42" s="15"/>
     </row>
     <row r="43" spans="1:8">
-      <c r="A43" s="84"/>
+      <c r="A43" s="89"/>
       <c r="B43" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="C43" s="72"/>
+      <c r="C43" s="73"/>
       <c r="D43" s="5">
         <v>1</v>
       </c>
-      <c r="E43" s="72"/>
+      <c r="E43" s="73"/>
       <c r="F43" s="5" t="s">
         <v>225</v>
       </c>
@@ -2610,31 +2616,31 @@
       <c r="H43" s="57"/>
     </row>
     <row r="44" spans="1:8">
-      <c r="A44" s="84"/>
+      <c r="A44" s="89"/>
       <c r="B44" s="7" t="s">
         <v>259</v>
       </c>
-      <c r="C44" s="72"/>
+      <c r="C44" s="73"/>
       <c r="D44" s="58">
         <v>1</v>
       </c>
-      <c r="E44" s="72"/>
+      <c r="E44" s="73"/>
       <c r="F44" s="59" t="s">
         <v>225</v>
       </c>
-      <c r="G44" s="20"/>
-      <c r="H44" s="20"/>
+      <c r="G44" s="40"/>
+      <c r="H44" s="40"/>
     </row>
     <row r="45" spans="1:8">
-      <c r="A45" s="84"/>
+      <c r="A45" s="89"/>
       <c r="B45" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C45" s="72"/>
+      <c r="C45" s="73"/>
       <c r="D45" s="5">
         <v>1</v>
       </c>
-      <c r="E45" s="72"/>
+      <c r="E45" s="73"/>
       <c r="F45" s="5" t="s">
         <v>225</v>
       </c>
@@ -2642,15 +2648,15 @@
       <c r="H45" s="30"/>
     </row>
     <row r="46" spans="1:8">
-      <c r="A46" s="84"/>
+      <c r="A46" s="89"/>
       <c r="B46" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="C46" s="72"/>
+      <c r="C46" s="73"/>
       <c r="D46" s="5">
         <v>1</v>
       </c>
-      <c r="E46" s="72"/>
+      <c r="E46" s="73"/>
       <c r="F46" s="5" t="s">
         <v>225</v>
       </c>
@@ -2658,15 +2664,15 @@
       <c r="H46" s="15"/>
     </row>
     <row r="47" spans="1:8">
-      <c r="A47" s="84"/>
+      <c r="A47" s="89"/>
       <c r="B47" s="7" t="s">
         <v>250</v>
       </c>
-      <c r="C47" s="72"/>
+      <c r="C47" s="73"/>
       <c r="D47" s="5">
         <v>1</v>
       </c>
-      <c r="E47" s="72"/>
+      <c r="E47" s="73"/>
       <c r="F47" s="5" t="s">
         <v>225</v>
       </c>
@@ -2674,15 +2680,15 @@
       <c r="H47" s="15"/>
     </row>
     <row r="48" spans="1:8">
-      <c r="A48" s="84"/>
+      <c r="A48" s="89"/>
       <c r="B48" s="7" t="s">
         <v>251</v>
       </c>
-      <c r="C48" s="72"/>
+      <c r="C48" s="73"/>
       <c r="D48" s="5">
         <v>1</v>
       </c>
-      <c r="E48" s="72"/>
+      <c r="E48" s="73"/>
       <c r="F48" s="5" t="s">
         <v>225</v>
       </c>
@@ -2690,19 +2696,19 @@
       <c r="H48" s="15"/>
     </row>
     <row r="49" spans="1:8">
-      <c r="A49" s="84" t="s">
+      <c r="A49" s="89" t="s">
         <v>48</v>
       </c>
       <c r="B49" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="C49" s="72">
+      <c r="C49" s="73">
         <v>2</v>
       </c>
       <c r="D49" s="5">
         <v>0</v>
       </c>
-      <c r="E49" s="72" t="s">
+      <c r="E49" s="73" t="s">
         <v>225</v>
       </c>
       <c r="F49" s="5" t="s">
@@ -2712,15 +2718,15 @@
       <c r="H49" s="15"/>
     </row>
     <row r="50" spans="1:8">
-      <c r="A50" s="84"/>
+      <c r="A50" s="89"/>
       <c r="B50" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="C50" s="72"/>
+      <c r="C50" s="73"/>
       <c r="D50" s="5">
         <v>2</v>
       </c>
-      <c r="E50" s="72"/>
+      <c r="E50" s="73"/>
       <c r="F50" s="5" t="s">
         <v>225</v>
       </c>
@@ -2728,15 +2734,15 @@
       <c r="H50" s="15"/>
     </row>
     <row r="51" spans="1:8">
-      <c r="A51" s="84"/>
+      <c r="A51" s="89"/>
       <c r="B51" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C51" s="72"/>
+      <c r="C51" s="73"/>
       <c r="D51" s="5">
         <v>2</v>
       </c>
-      <c r="E51" s="72"/>
+      <c r="E51" s="73"/>
       <c r="F51" s="5" t="s">
         <v>225</v>
       </c>
@@ -2744,15 +2750,15 @@
       <c r="H51" s="15"/>
     </row>
     <row r="52" spans="1:8">
-      <c r="A52" s="84"/>
+      <c r="A52" s="89"/>
       <c r="B52" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="C52" s="72"/>
+      <c r="C52" s="73"/>
       <c r="D52" s="5">
         <v>2</v>
       </c>
-      <c r="E52" s="72"/>
+      <c r="E52" s="73"/>
       <c r="F52" s="5" t="s">
         <v>225</v>
       </c>
@@ -2760,15 +2766,15 @@
       <c r="H52" s="15"/>
     </row>
     <row r="53" spans="1:8">
-      <c r="A53" s="84"/>
+      <c r="A53" s="89"/>
       <c r="B53" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C53" s="72"/>
+      <c r="C53" s="73"/>
       <c r="D53" s="5">
         <v>2</v>
       </c>
-      <c r="E53" s="72"/>
+      <c r="E53" s="73"/>
       <c r="F53" s="5" t="s">
         <v>225</v>
       </c>
@@ -2776,19 +2782,19 @@
       <c r="H53" s="15"/>
     </row>
     <row r="54" spans="1:8">
-      <c r="A54" s="84" t="s">
+      <c r="A54" s="89" t="s">
         <v>240</v>
       </c>
       <c r="B54" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="C54" s="72">
+      <c r="C54" s="73">
         <v>2</v>
       </c>
       <c r="D54" s="5">
         <v>0</v>
       </c>
-      <c r="E54" s="72" t="s">
+      <c r="E54" s="73" t="s">
         <v>226</v>
       </c>
       <c r="F54" s="5" t="s">
@@ -2798,15 +2804,15 @@
       <c r="H54" s="9"/>
     </row>
     <row r="55" spans="1:8">
-      <c r="A55" s="84"/>
+      <c r="A55" s="89"/>
       <c r="B55" s="7" t="s">
         <v>241</v>
       </c>
-      <c r="C55" s="72"/>
+      <c r="C55" s="73"/>
       <c r="D55" s="5">
         <v>2</v>
       </c>
-      <c r="E55" s="72"/>
+      <c r="E55" s="73"/>
       <c r="F55" s="5" t="s">
         <v>226</v>
       </c>
@@ -2814,15 +2820,15 @@
       <c r="H55" s="9"/>
     </row>
     <row r="56" spans="1:8">
-      <c r="A56" s="84"/>
+      <c r="A56" s="89"/>
       <c r="B56" s="7" t="s">
         <v>244</v>
       </c>
-      <c r="C56" s="72"/>
+      <c r="C56" s="73"/>
       <c r="D56" s="5">
         <v>2</v>
       </c>
-      <c r="E56" s="72"/>
+      <c r="E56" s="73"/>
       <c r="F56" s="5" t="s">
         <v>226</v>
       </c>
@@ -2830,15 +2836,15 @@
       <c r="H56" s="9"/>
     </row>
     <row r="57" spans="1:8">
-      <c r="A57" s="84"/>
+      <c r="A57" s="89"/>
       <c r="B57" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="C57" s="72"/>
+      <c r="C57" s="73"/>
       <c r="D57" s="5">
         <v>2</v>
       </c>
-      <c r="E57" s="72"/>
+      <c r="E57" s="73"/>
       <c r="F57" s="5" t="s">
         <v>226</v>
       </c>
@@ -2846,15 +2852,15 @@
       <c r="H57" s="8"/>
     </row>
     <row r="58" spans="1:8">
-      <c r="A58" s="84"/>
+      <c r="A58" s="89"/>
       <c r="B58" s="7" t="s">
         <v>246</v>
       </c>
-      <c r="C58" s="72"/>
+      <c r="C58" s="73"/>
       <c r="D58" s="5">
         <v>2</v>
       </c>
-      <c r="E58" s="72"/>
+      <c r="E58" s="73"/>
       <c r="F58" s="5" t="s">
         <v>226</v>
       </c>
@@ -2862,15 +2868,15 @@
       <c r="H58" s="9"/>
     </row>
     <row r="59" spans="1:8">
-      <c r="A59" s="84"/>
+      <c r="A59" s="89"/>
       <c r="B59" s="7" t="s">
         <v>242</v>
       </c>
-      <c r="C59" s="72"/>
+      <c r="C59" s="73"/>
       <c r="D59" s="5">
         <v>2</v>
       </c>
-      <c r="E59" s="72"/>
+      <c r="E59" s="73"/>
       <c r="F59" s="35" t="s">
         <v>226</v>
       </c>
@@ -2878,15 +2884,15 @@
       <c r="H59" s="41"/>
     </row>
     <row r="60" spans="1:8">
-      <c r="A60" s="84"/>
+      <c r="A60" s="89"/>
       <c r="B60" s="7" t="s">
         <v>247</v>
       </c>
-      <c r="C60" s="72"/>
+      <c r="C60" s="73"/>
       <c r="D60" s="5">
         <v>0</v>
       </c>
-      <c r="E60" s="73"/>
+      <c r="E60" s="75"/>
       <c r="F60" s="38" t="s">
         <v>226</v>
       </c>
@@ -2894,15 +2900,15 @@
       <c r="H60" s="40"/>
     </row>
     <row r="61" spans="1:8">
-      <c r="A61" s="84"/>
+      <c r="A61" s="89"/>
       <c r="B61" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="C61" s="72"/>
+      <c r="C61" s="73"/>
       <c r="D61" s="36">
         <v>2</v>
       </c>
-      <c r="E61" s="73"/>
+      <c r="E61" s="75"/>
       <c r="F61" s="37" t="s">
         <v>226</v>
       </c>
@@ -2910,19 +2916,19 @@
       <c r="H61" s="40"/>
     </row>
     <row r="62" spans="1:8">
-      <c r="A62" s="84" t="s">
+      <c r="A62" s="89" t="s">
         <v>55</v>
       </c>
       <c r="B62" s="7" t="s">
         <v>227</v>
       </c>
-      <c r="C62" s="72">
+      <c r="C62" s="73">
         <v>2</v>
       </c>
       <c r="D62" s="5">
         <v>2</v>
       </c>
-      <c r="E62" s="72" t="s">
+      <c r="E62" s="73" t="s">
         <v>226</v>
       </c>
       <c r="F62" s="5" t="s">
@@ -2932,15 +2938,15 @@
       <c r="H62" s="30"/>
     </row>
     <row r="63" spans="1:8">
-      <c r="A63" s="84"/>
+      <c r="A63" s="89"/>
       <c r="B63" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="C63" s="72"/>
+      <c r="C63" s="73"/>
       <c r="D63" s="5">
         <v>2</v>
       </c>
-      <c r="E63" s="72"/>
+      <c r="E63" s="73"/>
       <c r="F63" s="5" t="s">
         <v>226</v>
       </c>
@@ -2948,15 +2954,15 @@
       <c r="H63" s="15"/>
     </row>
     <row r="64" spans="1:8">
-      <c r="A64" s="84"/>
+      <c r="A64" s="89"/>
       <c r="B64" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="C64" s="72"/>
+      <c r="C64" s="73"/>
       <c r="D64" s="5">
         <v>2</v>
       </c>
-      <c r="E64" s="72"/>
+      <c r="E64" s="73"/>
       <c r="F64" s="5" t="s">
         <v>226</v>
       </c>
@@ -2964,15 +2970,15 @@
       <c r="H64" s="15"/>
     </row>
     <row r="65" spans="1:8">
-      <c r="A65" s="84"/>
+      <c r="A65" s="89"/>
       <c r="B65" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="C65" s="72"/>
+      <c r="C65" s="73"/>
       <c r="D65" s="5">
         <v>2</v>
       </c>
-      <c r="E65" s="72"/>
+      <c r="E65" s="73"/>
       <c r="F65" s="5" t="s">
         <v>226</v>
       </c>
@@ -2980,15 +2986,15 @@
       <c r="H65" s="15"/>
     </row>
     <row r="66" spans="1:8">
-      <c r="A66" s="84"/>
+      <c r="A66" s="89"/>
       <c r="B66" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="C66" s="72"/>
+      <c r="C66" s="73"/>
       <c r="D66" s="5">
         <v>2</v>
       </c>
-      <c r="E66" s="72"/>
+      <c r="E66" s="73"/>
       <c r="F66" s="5" t="s">
         <v>226</v>
       </c>
@@ -2996,15 +3002,15 @@
       <c r="H66" s="28"/>
     </row>
     <row r="67" spans="1:8">
-      <c r="A67" s="84"/>
+      <c r="A67" s="89"/>
       <c r="B67" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="C67" s="72"/>
+      <c r="C67" s="73"/>
       <c r="D67" s="5">
         <v>2</v>
       </c>
-      <c r="E67" s="72"/>
+      <c r="E67" s="73"/>
       <c r="F67" s="5" t="s">
         <v>226</v>
       </c>
@@ -3012,19 +3018,19 @@
       <c r="H67" s="28"/>
     </row>
     <row r="68" spans="1:8">
-      <c r="A68" s="85" t="s">
+      <c r="A68" s="90" t="s">
         <v>61</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="C68" s="72">
+      <c r="C68" s="73">
         <v>2</v>
       </c>
       <c r="D68" s="5">
         <v>2</v>
       </c>
-      <c r="E68" s="72" t="s">
+      <c r="E68" s="73" t="s">
         <v>225</v>
       </c>
       <c r="F68" s="5" t="s">
@@ -3034,15 +3040,15 @@
       <c r="H68" s="15"/>
     </row>
     <row r="69" spans="1:8">
-      <c r="A69" s="85"/>
+      <c r="A69" s="90"/>
       <c r="B69" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="C69" s="72"/>
+      <c r="C69" s="73"/>
       <c r="D69" s="5">
         <v>2</v>
       </c>
-      <c r="E69" s="72"/>
+      <c r="E69" s="73"/>
       <c r="F69" s="5" t="s">
         <v>225</v>
       </c>
@@ -3050,19 +3056,19 @@
       <c r="H69" s="15"/>
     </row>
     <row r="70" spans="1:8">
-      <c r="A70" s="86" t="s">
+      <c r="A70" s="91" t="s">
         <v>238</v>
       </c>
       <c r="B70" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="C70" s="69">
+      <c r="C70" s="70">
         <v>2</v>
       </c>
       <c r="D70" s="5">
         <v>0</v>
       </c>
-      <c r="E70" s="69" t="s">
+      <c r="E70" s="70" t="s">
         <v>225</v>
       </c>
       <c r="F70" s="5" t="s">
@@ -3072,15 +3078,15 @@
       <c r="H70" s="63"/>
     </row>
     <row r="71" spans="1:8">
-      <c r="A71" s="86"/>
+      <c r="A71" s="91"/>
       <c r="B71" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="C71" s="70"/>
+      <c r="C71" s="71"/>
       <c r="D71" s="5">
         <v>0</v>
       </c>
-      <c r="E71" s="70"/>
+      <c r="E71" s="71"/>
       <c r="F71" s="5" t="s">
         <v>226</v>
       </c>
@@ -3088,79 +3094,79 @@
       <c r="H71" s="40"/>
     </row>
     <row r="72" spans="1:8">
-      <c r="A72" s="86"/>
+      <c r="A72" s="91"/>
       <c r="B72" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="C72" s="70"/>
+      <c r="C72" s="71"/>
       <c r="D72" s="5">
         <v>1</v>
       </c>
-      <c r="E72" s="70"/>
+      <c r="E72" s="71"/>
       <c r="F72" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="G72" s="5"/>
-      <c r="H72" s="64"/>
+      <c r="G72" s="14"/>
+      <c r="H72" s="30"/>
     </row>
     <row r="73" spans="1:8">
-      <c r="A73" s="86"/>
+      <c r="A73" s="91"/>
       <c r="B73" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="C73" s="70"/>
+      <c r="C73" s="71"/>
       <c r="D73" s="5">
         <v>1</v>
       </c>
-      <c r="E73" s="70"/>
+      <c r="E73" s="71"/>
       <c r="F73" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="G73" s="5"/>
-      <c r="H73" s="6"/>
+      <c r="G73" s="14"/>
+      <c r="H73" s="15"/>
     </row>
     <row r="74" spans="1:8">
-      <c r="A74" s="86"/>
+      <c r="A74" s="91"/>
       <c r="B74" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="C74" s="70"/>
+      <c r="C74" s="71"/>
       <c r="D74" s="5">
         <v>1</v>
       </c>
-      <c r="E74" s="70"/>
+      <c r="E74" s="71"/>
       <c r="F74" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="G74" s="5"/>
-      <c r="H74" s="6"/>
+      <c r="G74" s="14"/>
+      <c r="H74" s="15"/>
     </row>
     <row r="75" spans="1:8">
-      <c r="A75" s="86"/>
+      <c r="A75" s="91"/>
       <c r="B75" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C75" s="70"/>
+      <c r="C75" s="71"/>
       <c r="D75" s="5">
         <v>0</v>
       </c>
-      <c r="E75" s="70"/>
+      <c r="E75" s="71"/>
       <c r="F75" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="G75" s="5"/>
-      <c r="H75" s="6"/>
+      <c r="G75" s="14"/>
+      <c r="H75" s="15"/>
     </row>
     <row r="76" spans="1:8">
-      <c r="A76" s="86"/>
+      <c r="A76" s="91"/>
       <c r="B76" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="C76" s="70"/>
+      <c r="C76" s="71"/>
       <c r="D76" s="5">
         <v>1</v>
       </c>
-      <c r="E76" s="70"/>
+      <c r="E76" s="71"/>
       <c r="F76" s="5" t="s">
         <v>225</v>
       </c>
@@ -3168,15 +3174,15 @@
       <c r="H76" s="6"/>
     </row>
     <row r="77" spans="1:8">
-      <c r="A77" s="86"/>
+      <c r="A77" s="91"/>
       <c r="B77" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="C77" s="70"/>
+      <c r="C77" s="71"/>
       <c r="D77" s="5">
         <v>1</v>
       </c>
-      <c r="E77" s="70"/>
+      <c r="E77" s="71"/>
       <c r="F77" s="5" t="s">
         <v>226</v>
       </c>
@@ -3184,15 +3190,15 @@
       <c r="H77" s="6"/>
     </row>
     <row r="78" spans="1:8">
-      <c r="A78" s="86"/>
+      <c r="A78" s="91"/>
       <c r="B78" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="C78" s="70"/>
+      <c r="C78" s="71"/>
       <c r="D78" s="5">
         <v>1</v>
       </c>
-      <c r="E78" s="70"/>
+      <c r="E78" s="71"/>
       <c r="F78" s="5" t="s">
         <v>226</v>
       </c>
@@ -3200,15 +3206,15 @@
       <c r="H78" s="6"/>
     </row>
     <row r="79" spans="1:8">
-      <c r="A79" s="86"/>
+      <c r="A79" s="91"/>
       <c r="B79" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C79" s="70"/>
+      <c r="C79" s="71"/>
       <c r="D79" s="5">
         <v>2</v>
       </c>
-      <c r="E79" s="70"/>
+      <c r="E79" s="71"/>
       <c r="F79" s="5" t="s">
         <v>252</v>
       </c>
@@ -3216,15 +3222,15 @@
       <c r="H79" s="6"/>
     </row>
     <row r="80" spans="1:8">
-      <c r="A80" s="86"/>
+      <c r="A80" s="91"/>
       <c r="B80" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="C80" s="70"/>
+      <c r="C80" s="71"/>
       <c r="D80" s="5">
         <v>1</v>
       </c>
-      <c r="E80" s="70"/>
+      <c r="E80" s="71"/>
       <c r="F80" s="5" t="s">
         <v>226</v>
       </c>
@@ -3232,15 +3238,15 @@
       <c r="H80" s="6"/>
     </row>
     <row r="81" spans="1:8">
-      <c r="A81" s="86"/>
+      <c r="A81" s="91"/>
       <c r="B81" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="C81" s="71"/>
+      <c r="C81" s="72"/>
       <c r="D81" s="5">
         <v>1</v>
       </c>
-      <c r="E81" s="71"/>
+      <c r="E81" s="72"/>
       <c r="F81" s="5" t="s">
         <v>252</v>
       </c>
@@ -3248,19 +3254,19 @@
       <c r="H81" s="6"/>
     </row>
     <row r="82" spans="1:8">
-      <c r="A82" s="86" t="s">
+      <c r="A82" s="91" t="s">
         <v>76</v>
       </c>
       <c r="B82" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C82" s="69">
+      <c r="C82" s="70">
         <v>4</v>
       </c>
       <c r="D82" s="5">
         <v>0</v>
       </c>
-      <c r="E82" s="69" t="s">
+      <c r="E82" s="70" t="s">
         <v>226</v>
       </c>
       <c r="F82" s="5" t="s">
@@ -3270,15 +3276,15 @@
       <c r="H82" s="6"/>
     </row>
     <row r="83" spans="1:8">
-      <c r="A83" s="86"/>
+      <c r="A83" s="91"/>
       <c r="B83" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="C83" s="70"/>
+      <c r="C83" s="71"/>
       <c r="D83" s="5">
         <v>1</v>
       </c>
-      <c r="E83" s="70"/>
+      <c r="E83" s="71"/>
       <c r="F83" s="5" t="s">
         <v>225</v>
       </c>
@@ -3286,15 +3292,15 @@
       <c r="H83" s="6"/>
     </row>
     <row r="84" spans="1:8">
-      <c r="A84" s="86"/>
+      <c r="A84" s="91"/>
       <c r="B84" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C84" s="70"/>
+      <c r="C84" s="71"/>
       <c r="D84" s="5">
         <v>2</v>
       </c>
-      <c r="E84" s="70"/>
+      <c r="E84" s="71"/>
       <c r="F84" s="5" t="s">
         <v>226</v>
       </c>
@@ -3302,15 +3308,15 @@
       <c r="H84" s="6"/>
     </row>
     <row r="85" spans="1:8">
-      <c r="A85" s="86"/>
+      <c r="A85" s="91"/>
       <c r="B85" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="C85" s="70"/>
+      <c r="C85" s="71"/>
       <c r="D85" s="5">
         <v>2</v>
       </c>
-      <c r="E85" s="70"/>
+      <c r="E85" s="71"/>
       <c r="F85" s="5" t="s">
         <v>226</v>
       </c>
@@ -3318,15 +3324,15 @@
       <c r="H85" s="6"/>
     </row>
     <row r="86" spans="1:8">
-      <c r="A86" s="86"/>
+      <c r="A86" s="91"/>
       <c r="B86" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="C86" s="70"/>
+      <c r="C86" s="71"/>
       <c r="D86" s="5">
         <v>2</v>
       </c>
-      <c r="E86" s="70"/>
+      <c r="E86" s="71"/>
       <c r="F86" s="5" t="s">
         <v>226</v>
       </c>
@@ -3334,15 +3340,15 @@
       <c r="H86" s="6"/>
     </row>
     <row r="87" spans="1:8">
-      <c r="A87" s="86"/>
+      <c r="A87" s="91"/>
       <c r="B87" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="C87" s="70"/>
+      <c r="C87" s="71"/>
       <c r="D87" s="5">
         <v>2</v>
       </c>
-      <c r="E87" s="70"/>
+      <c r="E87" s="71"/>
       <c r="F87" s="5" t="s">
         <v>252</v>
       </c>
@@ -3350,15 +3356,15 @@
       <c r="H87" s="6"/>
     </row>
     <row r="88" spans="1:8">
-      <c r="A88" s="86"/>
+      <c r="A88" s="91"/>
       <c r="B88" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="C88" s="70"/>
+      <c r="C88" s="71"/>
       <c r="D88" s="5">
         <v>2</v>
       </c>
-      <c r="E88" s="70"/>
+      <c r="E88" s="71"/>
       <c r="F88" s="5" t="s">
         <v>252</v>
       </c>
@@ -3366,15 +3372,15 @@
       <c r="H88" s="6"/>
     </row>
     <row r="89" spans="1:8">
-      <c r="A89" s="86"/>
+      <c r="A89" s="91"/>
       <c r="B89" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="C89" s="70"/>
+      <c r="C89" s="71"/>
       <c r="D89" s="5">
         <v>2</v>
       </c>
-      <c r="E89" s="70"/>
+      <c r="E89" s="71"/>
       <c r="F89" s="5" t="s">
         <v>252</v>
       </c>
@@ -3382,15 +3388,15 @@
       <c r="H89" s="6"/>
     </row>
     <row r="90" spans="1:8">
-      <c r="A90" s="86"/>
+      <c r="A90" s="91"/>
       <c r="B90" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="C90" s="71"/>
+      <c r="C90" s="72"/>
       <c r="D90" s="5">
         <v>4</v>
       </c>
-      <c r="E90" s="71"/>
+      <c r="E90" s="72"/>
       <c r="F90" s="5" t="s">
         <v>252</v>
       </c>
@@ -3398,19 +3404,19 @@
       <c r="H90" s="11"/>
     </row>
     <row r="91" spans="1:8">
-      <c r="A91" s="86" t="s">
+      <c r="A91" s="91" t="s">
         <v>86</v>
       </c>
       <c r="B91" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="C91" s="69">
+      <c r="C91" s="70">
         <v>2</v>
       </c>
       <c r="D91" s="5">
         <v>0</v>
       </c>
-      <c r="E91" s="69" t="s">
+      <c r="E91" s="70" t="s">
         <v>252</v>
       </c>
       <c r="F91" s="5" t="s">
@@ -3420,15 +3426,15 @@
       <c r="H91" s="6"/>
     </row>
     <row r="92" spans="1:8">
-      <c r="A92" s="86"/>
+      <c r="A92" s="91"/>
       <c r="B92" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="C92" s="70"/>
+      <c r="C92" s="71"/>
       <c r="D92" s="5">
         <v>1</v>
       </c>
-      <c r="E92" s="70"/>
+      <c r="E92" s="71"/>
       <c r="F92" s="5" t="s">
         <v>226</v>
       </c>
@@ -3436,15 +3442,15 @@
       <c r="H92" s="6"/>
     </row>
     <row r="93" spans="1:8">
-      <c r="A93" s="86"/>
+      <c r="A93" s="91"/>
       <c r="B93" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="C93" s="70"/>
+      <c r="C93" s="71"/>
       <c r="D93" s="5">
         <v>2</v>
       </c>
-      <c r="E93" s="70"/>
+      <c r="E93" s="71"/>
       <c r="F93" s="5" t="s">
         <v>252</v>
       </c>
@@ -3452,15 +3458,15 @@
       <c r="H93" s="6"/>
     </row>
     <row r="94" spans="1:8">
-      <c r="A94" s="86"/>
+      <c r="A94" s="91"/>
       <c r="B94" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="C94" s="70"/>
+      <c r="C94" s="71"/>
       <c r="D94" s="5">
         <v>1</v>
       </c>
-      <c r="E94" s="70"/>
+      <c r="E94" s="71"/>
       <c r="F94" s="5" t="s">
         <v>225</v>
       </c>
@@ -3468,15 +3474,15 @@
       <c r="H94" s="6"/>
     </row>
     <row r="95" spans="1:8">
-      <c r="A95" s="86"/>
+      <c r="A95" s="91"/>
       <c r="B95" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="C95" s="70"/>
+      <c r="C95" s="71"/>
       <c r="D95" s="5">
         <v>1</v>
       </c>
-      <c r="E95" s="70"/>
+      <c r="E95" s="71"/>
       <c r="F95" s="5" t="s">
         <v>226</v>
       </c>
@@ -3484,15 +3490,15 @@
       <c r="H95" s="6"/>
     </row>
     <row r="96" spans="1:8">
-      <c r="A96" s="86"/>
+      <c r="A96" s="91"/>
       <c r="B96" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="C96" s="70"/>
+      <c r="C96" s="71"/>
       <c r="D96" s="5">
         <v>2</v>
       </c>
-      <c r="E96" s="70"/>
+      <c r="E96" s="71"/>
       <c r="F96" s="5" t="s">
         <v>226</v>
       </c>
@@ -3500,15 +3506,15 @@
       <c r="H96" s="6"/>
     </row>
     <row r="97" spans="1:8">
-      <c r="A97" s="86"/>
+      <c r="A97" s="91"/>
       <c r="B97" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="C97" s="70"/>
+      <c r="C97" s="71"/>
       <c r="D97" s="5">
         <v>2</v>
       </c>
-      <c r="E97" s="70"/>
+      <c r="E97" s="71"/>
       <c r="F97" s="5" t="s">
         <v>226</v>
       </c>
@@ -3516,15 +3522,15 @@
       <c r="H97" s="6"/>
     </row>
     <row r="98" spans="1:8">
-      <c r="A98" s="86"/>
+      <c r="A98" s="91"/>
       <c r="B98" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="C98" s="70"/>
+      <c r="C98" s="71"/>
       <c r="D98" s="5">
         <v>2</v>
       </c>
-      <c r="E98" s="70"/>
+      <c r="E98" s="71"/>
       <c r="F98" s="5" t="s">
         <v>252</v>
       </c>
@@ -3532,15 +3538,15 @@
       <c r="H98" s="6"/>
     </row>
     <row r="99" spans="1:8">
-      <c r="A99" s="86"/>
+      <c r="A99" s="91"/>
       <c r="B99" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="C99" s="71"/>
+      <c r="C99" s="72"/>
       <c r="D99" s="5">
         <v>2</v>
       </c>
-      <c r="E99" s="71"/>
+      <c r="E99" s="72"/>
       <c r="F99" s="5" t="s">
         <v>252</v>
       </c>
@@ -3548,19 +3554,19 @@
       <c r="H99" s="6"/>
     </row>
     <row r="100" spans="1:8">
-      <c r="A100" s="86" t="s">
+      <c r="A100" s="91" t="s">
         <v>96</v>
       </c>
       <c r="B100" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="C100" s="69">
+      <c r="C100" s="70">
         <v>2</v>
       </c>
       <c r="D100" s="5">
         <v>2</v>
       </c>
-      <c r="E100" s="69" t="s">
+      <c r="E100" s="70" t="s">
         <v>226</v>
       </c>
       <c r="F100" s="5" t="s">
@@ -3570,15 +3576,15 @@
       <c r="H100" s="6"/>
     </row>
     <row r="101" spans="1:8">
-      <c r="A101" s="86"/>
+      <c r="A101" s="91"/>
       <c r="B101" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="C101" s="70"/>
+      <c r="C101" s="71"/>
       <c r="D101" s="5">
         <v>2</v>
       </c>
-      <c r="E101" s="70"/>
+      <c r="E101" s="71"/>
       <c r="F101" s="5" t="s">
         <v>226</v>
       </c>
@@ -3586,15 +3592,15 @@
       <c r="H101" s="6"/>
     </row>
     <row r="102" spans="1:8">
-      <c r="A102" s="86"/>
+      <c r="A102" s="91"/>
       <c r="B102" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="C102" s="70"/>
+      <c r="C102" s="71"/>
       <c r="D102" s="5">
         <v>2</v>
       </c>
-      <c r="E102" s="70"/>
+      <c r="E102" s="71"/>
       <c r="F102" s="5" t="s">
         <v>226</v>
       </c>
@@ -3602,15 +3608,15 @@
       <c r="H102" s="6"/>
     </row>
     <row r="103" spans="1:8">
-      <c r="A103" s="86"/>
+      <c r="A103" s="91"/>
       <c r="B103" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="C103" s="70"/>
+      <c r="C103" s="71"/>
       <c r="D103" s="5">
         <v>2</v>
       </c>
-      <c r="E103" s="70"/>
+      <c r="E103" s="71"/>
       <c r="F103" s="5" t="s">
         <v>226</v>
       </c>
@@ -3618,15 +3624,15 @@
       <c r="H103" s="6"/>
     </row>
     <row r="104" spans="1:8">
-      <c r="A104" s="86"/>
+      <c r="A104" s="91"/>
       <c r="B104" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="C104" s="71"/>
+      <c r="C104" s="72"/>
       <c r="D104" s="5">
         <v>2</v>
       </c>
-      <c r="E104" s="71"/>
+      <c r="E104" s="72"/>
       <c r="F104" s="5" t="s">
         <v>226</v>
       </c>
@@ -3634,19 +3640,19 @@
       <c r="H104" s="6"/>
     </row>
     <row r="105" spans="1:8">
-      <c r="A105" s="86" t="s">
+      <c r="A105" s="91" t="s">
         <v>102</v>
       </c>
       <c r="B105" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="C105" s="69">
+      <c r="C105" s="70">
         <v>3</v>
       </c>
       <c r="D105" s="5">
         <v>0</v>
       </c>
-      <c r="E105" s="69" t="s">
+      <c r="E105" s="70" t="s">
         <v>252</v>
       </c>
       <c r="F105" s="5" t="s">
@@ -3656,15 +3662,15 @@
       <c r="H105" s="6"/>
     </row>
     <row r="106" spans="1:8">
-      <c r="A106" s="86"/>
+      <c r="A106" s="91"/>
       <c r="B106" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="C106" s="70"/>
+      <c r="C106" s="71"/>
       <c r="D106" s="5">
         <v>3</v>
       </c>
-      <c r="E106" s="70"/>
+      <c r="E106" s="71"/>
       <c r="F106" s="5" t="s">
         <v>226</v>
       </c>
@@ -3672,15 +3678,15 @@
       <c r="H106" s="6"/>
     </row>
     <row r="107" spans="1:8">
-      <c r="A107" s="86"/>
+      <c r="A107" s="91"/>
       <c r="B107" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="C107" s="70"/>
+      <c r="C107" s="71"/>
       <c r="D107" s="5">
         <v>3</v>
       </c>
-      <c r="E107" s="70"/>
+      <c r="E107" s="71"/>
       <c r="F107" s="5" t="s">
         <v>226</v>
       </c>
@@ -3688,15 +3694,15 @@
       <c r="H107" s="6"/>
     </row>
     <row r="108" spans="1:8">
-      <c r="A108" s="86"/>
+      <c r="A108" s="91"/>
       <c r="B108" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="C108" s="70"/>
+      <c r="C108" s="71"/>
       <c r="D108" s="5">
         <v>3</v>
       </c>
-      <c r="E108" s="70"/>
+      <c r="E108" s="71"/>
       <c r="F108" s="5" t="s">
         <v>226</v>
       </c>
@@ -3704,15 +3710,15 @@
       <c r="H108" s="6"/>
     </row>
     <row r="109" spans="1:8">
-      <c r="A109" s="86"/>
+      <c r="A109" s="91"/>
       <c r="B109" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="C109" s="70"/>
+      <c r="C109" s="71"/>
       <c r="D109" s="5">
         <v>3</v>
       </c>
-      <c r="E109" s="70"/>
+      <c r="E109" s="71"/>
       <c r="F109" s="5" t="s">
         <v>252</v>
       </c>
@@ -3720,15 +3726,15 @@
       <c r="H109" s="6"/>
     </row>
     <row r="110" spans="1:8">
-      <c r="A110" s="86"/>
+      <c r="A110" s="91"/>
       <c r="B110" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="C110" s="71"/>
+      <c r="C110" s="72"/>
       <c r="D110" s="5">
         <v>3</v>
       </c>
-      <c r="E110" s="71"/>
+      <c r="E110" s="72"/>
       <c r="F110" s="5" t="s">
         <v>252</v>
       </c>
@@ -3736,19 +3742,19 @@
       <c r="H110" s="6"/>
     </row>
     <row r="111" spans="1:8">
-      <c r="A111" s="86" t="s">
+      <c r="A111" s="91" t="s">
         <v>109</v>
       </c>
       <c r="B111" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="C111" s="69">
+      <c r="C111" s="70">
         <v>3</v>
       </c>
       <c r="D111" s="5">
         <v>0</v>
       </c>
-      <c r="E111" s="69" t="s">
+      <c r="E111" s="70" t="s">
         <v>252</v>
       </c>
       <c r="F111" s="5" t="s">
@@ -3758,15 +3764,15 @@
       <c r="H111" s="6"/>
     </row>
     <row r="112" spans="1:8">
-      <c r="A112" s="86"/>
+      <c r="A112" s="91"/>
       <c r="B112" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="C112" s="70"/>
+      <c r="C112" s="71"/>
       <c r="D112" s="5">
         <v>3</v>
       </c>
-      <c r="E112" s="70"/>
+      <c r="E112" s="71"/>
       <c r="F112" s="5" t="s">
         <v>252</v>
       </c>
@@ -3774,15 +3780,15 @@
       <c r="H112" s="6"/>
     </row>
     <row r="113" spans="1:8">
-      <c r="A113" s="86"/>
+      <c r="A113" s="91"/>
       <c r="B113" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="C113" s="70"/>
+      <c r="C113" s="71"/>
       <c r="D113" s="5">
         <v>3</v>
       </c>
-      <c r="E113" s="70"/>
+      <c r="E113" s="71"/>
       <c r="F113" s="5" t="s">
         <v>252</v>
       </c>
@@ -3790,15 +3796,15 @@
       <c r="H113" s="6"/>
     </row>
     <row r="114" spans="1:8">
-      <c r="A114" s="86"/>
+      <c r="A114" s="91"/>
       <c r="B114" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="C114" s="70"/>
+      <c r="C114" s="71"/>
       <c r="D114" s="5">
         <v>3</v>
       </c>
-      <c r="E114" s="70"/>
+      <c r="E114" s="71"/>
       <c r="F114" s="5" t="s">
         <v>252</v>
       </c>
@@ -3806,15 +3812,15 @@
       <c r="H114" s="6"/>
     </row>
     <row r="115" spans="1:8">
-      <c r="A115" s="86"/>
+      <c r="A115" s="91"/>
       <c r="B115" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="C115" s="71"/>
+      <c r="C115" s="72"/>
       <c r="D115" s="5">
         <v>3</v>
       </c>
-      <c r="E115" s="71"/>
+      <c r="E115" s="72"/>
       <c r="F115" s="5" t="s">
         <v>252</v>
       </c>
@@ -3822,19 +3828,19 @@
       <c r="H115" s="6"/>
     </row>
     <row r="116" spans="1:8">
-      <c r="A116" s="78" t="s">
+      <c r="A116" s="79" t="s">
         <v>115</v>
       </c>
       <c r="B116" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="C116" s="69">
+      <c r="C116" s="70">
         <v>1</v>
       </c>
       <c r="D116" s="5">
         <v>0</v>
       </c>
-      <c r="E116" s="69" t="s">
+      <c r="E116" s="70" t="s">
         <v>225</v>
       </c>
       <c r="F116" s="5" t="s">
@@ -3844,15 +3850,15 @@
       <c r="H116" s="13"/>
     </row>
     <row r="117" spans="1:8">
-      <c r="A117" s="78"/>
+      <c r="A117" s="79"/>
       <c r="B117" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="C117" s="70"/>
+      <c r="C117" s="71"/>
       <c r="D117" s="5">
         <v>0</v>
       </c>
-      <c r="E117" s="70"/>
+      <c r="E117" s="71"/>
       <c r="F117" s="5" t="s">
         <v>225</v>
       </c>
@@ -3860,15 +3866,15 @@
       <c r="H117" s="15"/>
     </row>
     <row r="118" spans="1:8">
-      <c r="A118" s="78"/>
+      <c r="A118" s="79"/>
       <c r="B118" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C118" s="70"/>
+      <c r="C118" s="71"/>
       <c r="D118" s="5">
         <v>0</v>
       </c>
-      <c r="E118" s="70"/>
+      <c r="E118" s="71"/>
       <c r="F118" s="5" t="s">
         <v>225</v>
       </c>
@@ -3876,15 +3882,15 @@
       <c r="H118" s="13"/>
     </row>
     <row r="119" spans="1:8">
-      <c r="A119" s="78"/>
+      <c r="A119" s="79"/>
       <c r="B119" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="C119" s="70"/>
+      <c r="C119" s="71"/>
       <c r="D119" s="5">
         <v>1</v>
       </c>
-      <c r="E119" s="70"/>
+      <c r="E119" s="71"/>
       <c r="F119" s="5" t="s">
         <v>223</v>
       </c>
@@ -3892,15 +3898,15 @@
       <c r="H119" s="6"/>
     </row>
     <row r="120" spans="1:8">
-      <c r="A120" s="78"/>
+      <c r="A120" s="79"/>
       <c r="B120" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="C120" s="70"/>
+      <c r="C120" s="71"/>
       <c r="D120" s="5">
         <v>0</v>
       </c>
-      <c r="E120" s="70"/>
+      <c r="E120" s="71"/>
       <c r="F120" s="5" t="s">
         <v>223</v>
       </c>
@@ -3908,15 +3914,15 @@
       <c r="H120" s="6"/>
     </row>
     <row r="121" spans="1:8">
-      <c r="A121" s="78"/>
+      <c r="A121" s="79"/>
       <c r="B121" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="C121" s="70"/>
+      <c r="C121" s="71"/>
       <c r="D121" s="5">
         <v>0</v>
       </c>
-      <c r="E121" s="70"/>
+      <c r="E121" s="71"/>
       <c r="F121" s="5" t="s">
         <v>223</v>
       </c>
@@ -3924,15 +3930,15 @@
       <c r="H121" s="6"/>
     </row>
     <row r="122" spans="1:8">
-      <c r="A122" s="78"/>
+      <c r="A122" s="79"/>
       <c r="B122" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="C122" s="71"/>
+      <c r="C122" s="72"/>
       <c r="D122" s="5">
         <v>1</v>
       </c>
-      <c r="E122" s="71"/>
+      <c r="E122" s="72"/>
       <c r="F122" s="5" t="s">
         <v>225</v>
       </c>
@@ -3940,19 +3946,19 @@
       <c r="H122" s="6"/>
     </row>
     <row r="123" spans="1:8">
-      <c r="A123" s="78" t="s">
+      <c r="A123" s="79" t="s">
         <v>121</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="C123" s="69">
+      <c r="C123" s="70">
         <v>1</v>
       </c>
       <c r="D123" s="5">
         <v>1</v>
       </c>
-      <c r="E123" s="69" t="s">
+      <c r="E123" s="70" t="s">
         <v>225</v>
       </c>
       <c r="F123" s="5" t="s">
@@ -3962,15 +3968,15 @@
       <c r="H123" s="6"/>
     </row>
     <row r="124" spans="1:8">
-      <c r="A124" s="78"/>
+      <c r="A124" s="79"/>
       <c r="B124" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="C124" s="70"/>
+      <c r="C124" s="71"/>
       <c r="D124" s="5">
         <v>1</v>
       </c>
-      <c r="E124" s="70"/>
+      <c r="E124" s="71"/>
       <c r="F124" s="5" t="s">
         <v>225</v>
       </c>
@@ -3978,15 +3984,15 @@
       <c r="H124" s="6"/>
     </row>
     <row r="125" spans="1:8">
-      <c r="A125" s="78"/>
+      <c r="A125" s="79"/>
       <c r="B125" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="C125" s="70"/>
+      <c r="C125" s="71"/>
       <c r="D125" s="5">
         <v>1</v>
       </c>
-      <c r="E125" s="70"/>
+      <c r="E125" s="71"/>
       <c r="F125" s="5" t="s">
         <v>225</v>
       </c>
@@ -3994,15 +4000,15 @@
       <c r="H125" s="6"/>
     </row>
     <row r="126" spans="1:8">
-      <c r="A126" s="78"/>
+      <c r="A126" s="79"/>
       <c r="B126" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="C126" s="70"/>
+      <c r="C126" s="71"/>
       <c r="D126" s="5">
         <v>1</v>
       </c>
-      <c r="E126" s="70"/>
+      <c r="E126" s="71"/>
       <c r="F126" s="5" t="s">
         <v>226</v>
       </c>
@@ -4010,15 +4016,15 @@
       <c r="H126" s="6"/>
     </row>
     <row r="127" spans="1:8">
-      <c r="A127" s="78"/>
+      <c r="A127" s="79"/>
       <c r="B127" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="C127" s="70"/>
+      <c r="C127" s="71"/>
       <c r="D127" s="5">
         <v>1</v>
       </c>
-      <c r="E127" s="70"/>
+      <c r="E127" s="71"/>
       <c r="F127" s="5" t="s">
         <v>226</v>
       </c>
@@ -4026,15 +4032,15 @@
       <c r="H127" s="6"/>
     </row>
     <row r="128" spans="1:8">
-      <c r="A128" s="78"/>
+      <c r="A128" s="79"/>
       <c r="B128" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="C128" s="70"/>
+      <c r="C128" s="71"/>
       <c r="D128" s="5">
         <v>1</v>
       </c>
-      <c r="E128" s="70"/>
+      <c r="E128" s="71"/>
       <c r="F128" s="5" t="s">
         <v>226</v>
       </c>
@@ -4042,15 +4048,15 @@
       <c r="H128" s="6"/>
     </row>
     <row r="129" spans="1:8">
-      <c r="A129" s="78"/>
+      <c r="A129" s="79"/>
       <c r="B129" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="C129" s="70"/>
+      <c r="C129" s="71"/>
       <c r="D129" s="5">
         <v>1</v>
       </c>
-      <c r="E129" s="70"/>
+      <c r="E129" s="71"/>
       <c r="F129" s="5" t="s">
         <v>226</v>
       </c>
@@ -4058,15 +4064,15 @@
       <c r="H129" s="6"/>
     </row>
     <row r="130" spans="1:8">
-      <c r="A130" s="78"/>
+      <c r="A130" s="79"/>
       <c r="B130" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="C130" s="71"/>
+      <c r="C130" s="72"/>
       <c r="D130" s="5">
         <v>1</v>
       </c>
-      <c r="E130" s="71"/>
+      <c r="E130" s="72"/>
       <c r="F130" s="5" t="s">
         <v>226</v>
       </c>
@@ -4096,37 +4102,37 @@
       <c r="H131" s="6"/>
     </row>
     <row r="132" spans="1:8">
-      <c r="A132" s="95" t="s">
+      <c r="A132" s="85" t="s">
         <v>132</v>
       </c>
       <c r="B132" s="7" t="s">
         <v>262</v>
       </c>
-      <c r="C132" s="69">
+      <c r="C132" s="70">
         <v>4</v>
       </c>
       <c r="D132" s="67">
         <v>0</v>
       </c>
-      <c r="E132" s="69" t="s">
+      <c r="E132" s="70" t="s">
         <v>225</v>
       </c>
       <c r="F132" s="67" t="s">
         <v>225</v>
       </c>
-      <c r="G132" s="67"/>
-      <c r="H132" s="6"/>
+      <c r="G132" s="14"/>
+      <c r="H132" s="15"/>
     </row>
     <row r="133" spans="1:8">
-      <c r="A133" s="96"/>
+      <c r="A133" s="86"/>
       <c r="B133" s="7" t="s">
         <v>263</v>
       </c>
-      <c r="C133" s="71"/>
+      <c r="C133" s="72"/>
       <c r="D133" s="5">
         <v>4</v>
       </c>
-      <c r="E133" s="71"/>
+      <c r="E133" s="72"/>
       <c r="F133" s="5" t="s">
         <v>225</v>
       </c>
@@ -4134,19 +4140,19 @@
       <c r="H133" s="6"/>
     </row>
     <row r="134" spans="1:8">
-      <c r="A134" s="79" t="s">
+      <c r="A134" s="80" t="s">
         <v>133</v>
       </c>
       <c r="B134" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="C134" s="69">
+      <c r="C134" s="70">
         <v>3</v>
       </c>
       <c r="D134" s="5">
         <v>0</v>
       </c>
-      <c r="E134" s="69" t="s">
+      <c r="E134" s="70" t="s">
         <v>226</v>
       </c>
       <c r="F134" s="5" t="s">
@@ -4156,31 +4162,31 @@
       <c r="H134" s="15"/>
     </row>
     <row r="135" spans="1:8">
-      <c r="A135" s="79"/>
+      <c r="A135" s="80"/>
       <c r="B135" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="C135" s="70"/>
+      <c r="C135" s="71"/>
       <c r="D135" s="5">
         <v>0</v>
       </c>
-      <c r="E135" s="70"/>
+      <c r="E135" s="71"/>
       <c r="F135" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="G135" s="5"/>
+      <c r="G135" s="14"/>
       <c r="H135" s="15"/>
     </row>
     <row r="136" spans="1:8">
-      <c r="A136" s="79"/>
+      <c r="A136" s="80"/>
       <c r="B136" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="C136" s="70"/>
+      <c r="C136" s="71"/>
       <c r="D136" s="5">
         <v>1</v>
       </c>
-      <c r="E136" s="70"/>
+      <c r="E136" s="71"/>
       <c r="F136" s="5" t="s">
         <v>226</v>
       </c>
@@ -4188,31 +4194,31 @@
       <c r="H136" s="15"/>
     </row>
     <row r="137" spans="1:8">
-      <c r="A137" s="79"/>
+      <c r="A137" s="80"/>
       <c r="B137" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="C137" s="70"/>
+      <c r="C137" s="71"/>
       <c r="D137" s="5">
         <v>1</v>
       </c>
-      <c r="E137" s="70"/>
+      <c r="E137" s="71"/>
       <c r="F137" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="G137" s="5"/>
+      <c r="G137" s="14"/>
       <c r="H137" s="15"/>
     </row>
     <row r="138" spans="1:8">
-      <c r="A138" s="79"/>
+      <c r="A138" s="80"/>
       <c r="B138" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="C138" s="70"/>
+      <c r="C138" s="71"/>
       <c r="D138" s="5">
         <v>1</v>
       </c>
-      <c r="E138" s="70"/>
+      <c r="E138" s="71"/>
       <c r="F138" s="5" t="s">
         <v>226</v>
       </c>
@@ -4220,15 +4226,15 @@
       <c r="H138" s="28"/>
     </row>
     <row r="139" spans="1:8">
-      <c r="A139" s="79"/>
+      <c r="A139" s="80"/>
       <c r="B139" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="C139" s="70"/>
+      <c r="C139" s="71"/>
       <c r="D139" s="5">
         <v>1</v>
       </c>
-      <c r="E139" s="70"/>
+      <c r="E139" s="71"/>
       <c r="F139" s="5" t="s">
         <v>226</v>
       </c>
@@ -4236,15 +4242,15 @@
       <c r="H139" s="15"/>
     </row>
     <row r="140" spans="1:8">
-      <c r="A140" s="79"/>
+      <c r="A140" s="80"/>
       <c r="B140" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="C140" s="70"/>
+      <c r="C140" s="71"/>
       <c r="D140" s="5">
         <v>3</v>
       </c>
-      <c r="E140" s="70"/>
+      <c r="E140" s="71"/>
       <c r="F140" s="5" t="s">
         <v>226</v>
       </c>
@@ -4252,15 +4258,15 @@
       <c r="H140" s="15"/>
     </row>
     <row r="141" spans="1:8">
-      <c r="A141" s="79"/>
+      <c r="A141" s="80"/>
       <c r="B141" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="C141" s="71"/>
+      <c r="C141" s="72"/>
       <c r="D141" s="5">
         <v>3</v>
       </c>
-      <c r="E141" s="71"/>
+      <c r="E141" s="72"/>
       <c r="F141" s="5" t="s">
         <v>226</v>
       </c>
@@ -4268,19 +4274,19 @@
       <c r="H141" s="15"/>
     </row>
     <row r="142" spans="1:8">
-      <c r="A142" s="80" t="s">
+      <c r="A142" s="81" t="s">
         <v>141</v>
       </c>
       <c r="B142" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="C142" s="69">
+      <c r="C142" s="70">
         <v>2</v>
       </c>
       <c r="D142" s="5">
         <v>0</v>
       </c>
-      <c r="E142" s="69" t="s">
+      <c r="E142" s="70" t="s">
         <v>226</v>
       </c>
       <c r="F142" s="5" t="s">
@@ -4290,15 +4296,15 @@
       <c r="H142" s="15"/>
     </row>
     <row r="143" spans="1:8">
-      <c r="A143" s="80"/>
+      <c r="A143" s="81"/>
       <c r="B143" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="C143" s="70"/>
+      <c r="C143" s="71"/>
       <c r="D143" s="5">
         <v>2</v>
       </c>
-      <c r="E143" s="70"/>
+      <c r="E143" s="71"/>
       <c r="F143" s="5" t="s">
         <v>226</v>
       </c>
@@ -4306,15 +4312,15 @@
       <c r="H143" s="6"/>
     </row>
     <row r="144" spans="1:8">
-      <c r="A144" s="80"/>
+      <c r="A144" s="81"/>
       <c r="B144" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="C144" s="70"/>
+      <c r="C144" s="71"/>
       <c r="D144" s="5">
         <v>2</v>
       </c>
-      <c r="E144" s="70"/>
+      <c r="E144" s="71"/>
       <c r="F144" s="5" t="s">
         <v>226</v>
       </c>
@@ -4322,15 +4328,15 @@
       <c r="H144" s="6"/>
     </row>
     <row r="145" spans="1:8">
-      <c r="A145" s="80"/>
+      <c r="A145" s="81"/>
       <c r="B145" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="C145" s="70"/>
+      <c r="C145" s="71"/>
       <c r="D145" s="5">
         <v>2</v>
       </c>
-      <c r="E145" s="70"/>
+      <c r="E145" s="71"/>
       <c r="F145" s="5" t="s">
         <v>226</v>
       </c>
@@ -4338,15 +4344,15 @@
       <c r="H145" s="6"/>
     </row>
     <row r="146" spans="1:8">
-      <c r="A146" s="80"/>
+      <c r="A146" s="81"/>
       <c r="B146" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="C146" s="71"/>
+      <c r="C146" s="72"/>
       <c r="D146" s="5">
         <v>2</v>
       </c>
-      <c r="E146" s="71"/>
+      <c r="E146" s="72"/>
       <c r="F146" s="5" t="s">
         <v>226</v>
       </c>
@@ -4354,19 +4360,19 @@
       <c r="H146" s="6"/>
     </row>
     <row r="147" spans="1:8">
-      <c r="A147" s="80" t="s">
+      <c r="A147" s="81" t="s">
         <v>147</v>
       </c>
       <c r="B147" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="C147" s="69">
+      <c r="C147" s="70">
         <v>2</v>
       </c>
       <c r="D147" s="5">
         <v>0</v>
       </c>
-      <c r="E147" s="69" t="s">
+      <c r="E147" s="70" t="s">
         <v>226</v>
       </c>
       <c r="F147" s="5" t="s">
@@ -4376,15 +4382,15 @@
       <c r="H147" s="15"/>
     </row>
     <row r="148" spans="1:8">
-      <c r="A148" s="80"/>
+      <c r="A148" s="81"/>
       <c r="B148" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="C148" s="70"/>
+      <c r="C148" s="71"/>
       <c r="D148" s="5">
         <v>2</v>
       </c>
-      <c r="E148" s="70"/>
+      <c r="E148" s="71"/>
       <c r="F148" s="5" t="s">
         <v>226</v>
       </c>
@@ -4392,15 +4398,15 @@
       <c r="H148" s="6"/>
     </row>
     <row r="149" spans="1:8">
-      <c r="A149" s="80"/>
+      <c r="A149" s="81"/>
       <c r="B149" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="C149" s="70"/>
+      <c r="C149" s="71"/>
       <c r="D149" s="5">
         <v>2</v>
       </c>
-      <c r="E149" s="70"/>
+      <c r="E149" s="71"/>
       <c r="F149" s="5" t="s">
         <v>226</v>
       </c>
@@ -4408,15 +4414,15 @@
       <c r="H149" s="6"/>
     </row>
     <row r="150" spans="1:8">
-      <c r="A150" s="80"/>
+      <c r="A150" s="81"/>
       <c r="B150" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="C150" s="70"/>
+      <c r="C150" s="71"/>
       <c r="D150" s="5">
         <v>2</v>
       </c>
-      <c r="E150" s="70"/>
+      <c r="E150" s="71"/>
       <c r="F150" s="5" t="s">
         <v>226</v>
       </c>
@@ -4424,15 +4430,15 @@
       <c r="H150" s="6"/>
     </row>
     <row r="151" spans="1:8">
-      <c r="A151" s="80"/>
+      <c r="A151" s="81"/>
       <c r="B151" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="C151" s="70"/>
+      <c r="C151" s="71"/>
       <c r="D151" s="5">
         <v>2</v>
       </c>
-      <c r="E151" s="70"/>
+      <c r="E151" s="71"/>
       <c r="F151" s="5" t="s">
         <v>226</v>
       </c>
@@ -4440,15 +4446,15 @@
       <c r="H151" s="6"/>
     </row>
     <row r="152" spans="1:8">
-      <c r="A152" s="80"/>
+      <c r="A152" s="81"/>
       <c r="B152" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="C152" s="70"/>
+      <c r="C152" s="71"/>
       <c r="D152" s="5">
         <v>2</v>
       </c>
-      <c r="E152" s="70"/>
+      <c r="E152" s="71"/>
       <c r="F152" s="5" t="s">
         <v>226</v>
       </c>
@@ -4456,15 +4462,15 @@
       <c r="H152" s="6"/>
     </row>
     <row r="153" spans="1:8">
-      <c r="A153" s="80"/>
+      <c r="A153" s="81"/>
       <c r="B153" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="C153" s="71"/>
+      <c r="C153" s="72"/>
       <c r="D153" s="5">
         <v>2</v>
       </c>
-      <c r="E153" s="71"/>
+      <c r="E153" s="72"/>
       <c r="F153" s="5" t="s">
         <v>226</v>
       </c>
@@ -4472,19 +4478,19 @@
       <c r="H153" s="6"/>
     </row>
     <row r="154" spans="1:8" ht="18" customHeight="1">
-      <c r="A154" s="81" t="s">
+      <c r="A154" s="82" t="s">
         <v>154</v>
       </c>
       <c r="B154" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="C154" s="69">
+      <c r="C154" s="70">
         <v>2</v>
       </c>
       <c r="D154" s="5">
         <v>0</v>
       </c>
-      <c r="E154" s="69" t="s">
+      <c r="E154" s="70" t="s">
         <v>225</v>
       </c>
       <c r="F154" s="5" t="s">
@@ -4494,15 +4500,15 @@
       <c r="H154" s="6"/>
     </row>
     <row r="155" spans="1:8">
-      <c r="A155" s="81"/>
+      <c r="A155" s="82"/>
       <c r="B155" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="C155" s="70"/>
+      <c r="C155" s="71"/>
       <c r="D155" s="5">
         <v>2</v>
       </c>
-      <c r="E155" s="70"/>
+      <c r="E155" s="71"/>
       <c r="F155" s="5" t="s">
         <v>225</v>
       </c>
@@ -4510,15 +4516,15 @@
       <c r="H155" s="6"/>
     </row>
     <row r="156" spans="1:8">
-      <c r="A156" s="81"/>
+      <c r="A156" s="82"/>
       <c r="B156" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="C156" s="70"/>
+      <c r="C156" s="71"/>
       <c r="D156" s="5">
         <v>2</v>
       </c>
-      <c r="E156" s="70"/>
+      <c r="E156" s="71"/>
       <c r="F156" s="5" t="s">
         <v>225</v>
       </c>
@@ -4526,15 +4532,15 @@
       <c r="H156" s="6"/>
     </row>
     <row r="157" spans="1:8">
-      <c r="A157" s="81"/>
+      <c r="A157" s="82"/>
       <c r="B157" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="C157" s="70"/>
+      <c r="C157" s="71"/>
       <c r="D157" s="5">
         <v>2</v>
       </c>
-      <c r="E157" s="70"/>
+      <c r="E157" s="71"/>
       <c r="F157" s="5" t="s">
         <v>225</v>
       </c>
@@ -4542,15 +4548,15 @@
       <c r="H157" s="6"/>
     </row>
     <row r="158" spans="1:8">
-      <c r="A158" s="81"/>
+      <c r="A158" s="82"/>
       <c r="B158" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="C158" s="70"/>
+      <c r="C158" s="71"/>
       <c r="D158" s="5">
         <v>2</v>
       </c>
-      <c r="E158" s="70"/>
+      <c r="E158" s="71"/>
       <c r="F158" s="5" t="s">
         <v>226</v>
       </c>
@@ -4558,15 +4564,15 @@
       <c r="H158" s="6"/>
     </row>
     <row r="159" spans="1:8">
-      <c r="A159" s="81"/>
+      <c r="A159" s="82"/>
       <c r="B159" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="C159" s="71"/>
+      <c r="C159" s="72"/>
       <c r="D159" s="5">
         <v>2</v>
       </c>
-      <c r="E159" s="71"/>
+      <c r="E159" s="72"/>
       <c r="F159" s="5" t="s">
         <v>252</v>
       </c>
@@ -4574,19 +4580,19 @@
       <c r="H159" s="6"/>
     </row>
     <row r="160" spans="1:8">
-      <c r="A160" s="81" t="s">
+      <c r="A160" s="82" t="s">
         <v>161</v>
       </c>
       <c r="B160" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="C160" s="69">
+      <c r="C160" s="70">
         <v>2</v>
       </c>
       <c r="D160" s="5">
         <v>0</v>
       </c>
-      <c r="E160" s="69" t="s">
+      <c r="E160" s="70" t="s">
         <v>225</v>
       </c>
       <c r="F160" s="5" t="s">
@@ -4596,15 +4602,15 @@
       <c r="H160" s="6"/>
     </row>
     <row r="161" spans="1:8">
-      <c r="A161" s="81"/>
+      <c r="A161" s="82"/>
       <c r="B161" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="C161" s="70"/>
+      <c r="C161" s="71"/>
       <c r="D161" s="5">
         <v>2</v>
       </c>
-      <c r="E161" s="70"/>
+      <c r="E161" s="71"/>
       <c r="F161" s="5" t="s">
         <v>223</v>
       </c>
@@ -4612,15 +4618,15 @@
       <c r="H161" s="6"/>
     </row>
     <row r="162" spans="1:8">
-      <c r="A162" s="81"/>
+      <c r="A162" s="82"/>
       <c r="B162" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="C162" s="70"/>
+      <c r="C162" s="71"/>
       <c r="D162" s="5">
         <v>2</v>
       </c>
-      <c r="E162" s="70"/>
+      <c r="E162" s="71"/>
       <c r="F162" s="5" t="s">
         <v>225</v>
       </c>
@@ -4628,15 +4634,15 @@
       <c r="H162" s="6"/>
     </row>
     <row r="163" spans="1:8">
-      <c r="A163" s="81"/>
+      <c r="A163" s="82"/>
       <c r="B163" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="C163" s="71"/>
+      <c r="C163" s="72"/>
       <c r="D163" s="5">
         <v>2</v>
       </c>
-      <c r="E163" s="71"/>
+      <c r="E163" s="72"/>
       <c r="F163" s="5" t="s">
         <v>225</v>
       </c>
@@ -4644,19 +4650,19 @@
       <c r="H163" s="6"/>
     </row>
     <row r="164" spans="1:8">
-      <c r="A164" s="82" t="s">
+      <c r="A164" s="83" t="s">
         <v>166</v>
       </c>
       <c r="B164" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="C164" s="69">
+      <c r="C164" s="70">
         <v>1</v>
       </c>
       <c r="D164" s="5">
         <v>1</v>
       </c>
-      <c r="E164" s="69" t="s">
+      <c r="E164" s="70" t="s">
         <v>225</v>
       </c>
       <c r="F164" s="5" t="s">
@@ -4666,15 +4672,15 @@
       <c r="H164" s="15"/>
     </row>
     <row r="165" spans="1:8">
-      <c r="A165" s="82"/>
+      <c r="A165" s="83"/>
       <c r="B165" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="C165" s="70"/>
+      <c r="C165" s="71"/>
       <c r="D165" s="5">
         <v>0</v>
       </c>
-      <c r="E165" s="70"/>
+      <c r="E165" s="71"/>
       <c r="F165" s="5" t="s">
         <v>223</v>
       </c>
@@ -4682,15 +4688,15 @@
       <c r="H165" s="15"/>
     </row>
     <row r="166" spans="1:8">
-      <c r="A166" s="82"/>
+      <c r="A166" s="83"/>
       <c r="B166" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="C166" s="70"/>
+      <c r="C166" s="71"/>
       <c r="D166" s="5">
         <v>1</v>
       </c>
-      <c r="E166" s="70"/>
+      <c r="E166" s="71"/>
       <c r="F166" s="5" t="s">
         <v>223</v>
       </c>
@@ -4698,15 +4704,15 @@
       <c r="H166" s="15"/>
     </row>
     <row r="167" spans="1:8">
-      <c r="A167" s="82"/>
+      <c r="A167" s="83"/>
       <c r="B167" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C167" s="70"/>
+      <c r="C167" s="71"/>
       <c r="D167" s="5">
         <v>0</v>
       </c>
-      <c r="E167" s="70"/>
+      <c r="E167" s="71"/>
       <c r="F167" s="5" t="s">
         <v>223</v>
       </c>
@@ -4714,15 +4720,15 @@
       <c r="H167" s="13"/>
     </row>
     <row r="168" spans="1:8">
-      <c r="A168" s="82"/>
+      <c r="A168" s="83"/>
       <c r="B168" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="C168" s="70"/>
+      <c r="C168" s="71"/>
       <c r="D168" s="5">
         <v>1</v>
       </c>
-      <c r="E168" s="70"/>
+      <c r="E168" s="71"/>
       <c r="F168" s="5" t="s">
         <v>225</v>
       </c>
@@ -4730,15 +4736,15 @@
       <c r="H168" s="28"/>
     </row>
     <row r="169" spans="1:8">
-      <c r="A169" s="82"/>
+      <c r="A169" s="83"/>
       <c r="B169" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C169" s="71"/>
+      <c r="C169" s="72"/>
       <c r="D169" s="5">
         <v>0</v>
       </c>
-      <c r="E169" s="71"/>
+      <c r="E169" s="72"/>
       <c r="F169" s="5" t="s">
         <v>223</v>
       </c>
@@ -4746,19 +4752,19 @@
       <c r="H169" s="63"/>
     </row>
     <row r="170" spans="1:8">
-      <c r="A170" s="82" t="s">
+      <c r="A170" s="83" t="s">
         <v>170</v>
       </c>
       <c r="B170" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="C170" s="69">
+      <c r="C170" s="70">
         <v>1</v>
       </c>
       <c r="D170" s="5">
         <v>1</v>
       </c>
-      <c r="E170" s="69" t="s">
+      <c r="E170" s="70" t="s">
         <v>225</v>
       </c>
       <c r="F170" s="5" t="s">
@@ -4768,15 +4774,15 @@
       <c r="H170" s="20"/>
     </row>
     <row r="171" spans="1:8">
-      <c r="A171" s="82"/>
+      <c r="A171" s="83"/>
       <c r="B171" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="C171" s="71"/>
+      <c r="C171" s="72"/>
       <c r="D171" s="5">
         <v>1</v>
       </c>
-      <c r="E171" s="71"/>
+      <c r="E171" s="72"/>
       <c r="F171" s="5" t="s">
         <v>225</v>
       </c>
@@ -4828,19 +4834,19 @@
       <c r="H173" s="6"/>
     </row>
     <row r="174" spans="1:8">
-      <c r="A174" s="83" t="s">
+      <c r="A174" s="84" t="s">
         <v>175</v>
       </c>
       <c r="B174" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C174" s="69">
+      <c r="C174" s="70">
         <v>2</v>
       </c>
       <c r="D174" s="5">
         <v>0</v>
       </c>
-      <c r="E174" s="69" t="s">
+      <c r="E174" s="70" t="s">
         <v>225</v>
       </c>
       <c r="F174" s="5" t="s">
@@ -4850,15 +4856,15 @@
       <c r="H174" s="13"/>
     </row>
     <row r="175" spans="1:8">
-      <c r="A175" s="83"/>
+      <c r="A175" s="84"/>
       <c r="B175" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="C175" s="70"/>
+      <c r="C175" s="71"/>
       <c r="D175" s="5">
         <v>0</v>
       </c>
-      <c r="E175" s="70"/>
+      <c r="E175" s="71"/>
       <c r="F175" s="5" t="s">
         <v>225</v>
       </c>
@@ -4866,15 +4872,15 @@
       <c r="H175" s="6"/>
     </row>
     <row r="176" spans="1:8">
-      <c r="A176" s="83"/>
+      <c r="A176" s="84"/>
       <c r="B176" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="C176" s="70"/>
+      <c r="C176" s="71"/>
       <c r="D176" s="5">
         <v>2</v>
       </c>
-      <c r="E176" s="70"/>
+      <c r="E176" s="71"/>
       <c r="F176" s="5" t="s">
         <v>225</v>
       </c>
@@ -4882,15 +4888,15 @@
       <c r="H176" s="6"/>
     </row>
     <row r="177" spans="1:8">
-      <c r="A177" s="83"/>
+      <c r="A177" s="84"/>
       <c r="B177" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="C177" s="70"/>
+      <c r="C177" s="71"/>
       <c r="D177" s="5">
         <v>2</v>
       </c>
-      <c r="E177" s="70"/>
+      <c r="E177" s="71"/>
       <c r="F177" s="5" t="s">
         <v>225</v>
       </c>
@@ -4898,15 +4904,15 @@
       <c r="H177" s="6"/>
     </row>
     <row r="178" spans="1:8">
-      <c r="A178" s="83"/>
+      <c r="A178" s="84"/>
       <c r="B178" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="C178" s="70"/>
+      <c r="C178" s="71"/>
       <c r="D178" s="5">
         <v>2</v>
       </c>
-      <c r="E178" s="70"/>
+      <c r="E178" s="71"/>
       <c r="F178" s="5" t="s">
         <v>225</v>
       </c>
@@ -4914,15 +4920,15 @@
       <c r="H178" s="6"/>
     </row>
     <row r="179" spans="1:8">
-      <c r="A179" s="83"/>
+      <c r="A179" s="84"/>
       <c r="B179" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="C179" s="70"/>
+      <c r="C179" s="71"/>
       <c r="D179" s="5">
         <v>2</v>
       </c>
-      <c r="E179" s="70"/>
+      <c r="E179" s="71"/>
       <c r="F179" s="5" t="s">
         <v>225</v>
       </c>
@@ -4930,15 +4936,15 @@
       <c r="H179" s="6"/>
     </row>
     <row r="180" spans="1:8">
-      <c r="A180" s="83"/>
+      <c r="A180" s="84"/>
       <c r="B180" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="C180" s="70"/>
+      <c r="C180" s="71"/>
       <c r="D180" s="5">
         <v>2</v>
       </c>
-      <c r="E180" s="70"/>
+      <c r="E180" s="71"/>
       <c r="F180" s="5" t="s">
         <v>225</v>
       </c>
@@ -4946,15 +4952,15 @@
       <c r="H180" s="6"/>
     </row>
     <row r="181" spans="1:8">
-      <c r="A181" s="83"/>
+      <c r="A181" s="84"/>
       <c r="B181" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="C181" s="71"/>
+      <c r="C181" s="72"/>
       <c r="D181" s="5">
         <v>2</v>
       </c>
-      <c r="E181" s="71"/>
+      <c r="E181" s="72"/>
       <c r="F181" s="5" t="s">
         <v>225</v>
       </c>
@@ -5072,19 +5078,19 @@
       <c r="H186" s="11"/>
     </row>
     <row r="187" spans="1:8">
-      <c r="A187" s="76" t="s">
+      <c r="A187" s="77" t="s">
         <v>192</v>
       </c>
       <c r="B187" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="C187" s="69">
+      <c r="C187" s="70">
         <v>4</v>
       </c>
       <c r="D187" s="5">
         <v>4</v>
       </c>
-      <c r="E187" s="69" t="s">
+      <c r="E187" s="70" t="s">
         <v>226</v>
       </c>
       <c r="F187" s="5" t="s">
@@ -5094,15 +5100,15 @@
       <c r="H187" s="11"/>
     </row>
     <row r="188" spans="1:8">
-      <c r="A188" s="76"/>
+      <c r="A188" s="77"/>
       <c r="B188" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="C188" s="70"/>
+      <c r="C188" s="71"/>
       <c r="D188" s="5">
         <v>4</v>
       </c>
-      <c r="E188" s="70"/>
+      <c r="E188" s="71"/>
       <c r="F188" s="5" t="s">
         <v>226</v>
       </c>
@@ -5110,15 +5116,15 @@
       <c r="H188" s="11"/>
     </row>
     <row r="189" spans="1:8">
-      <c r="A189" s="76"/>
+      <c r="A189" s="77"/>
       <c r="B189" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="C189" s="70"/>
+      <c r="C189" s="71"/>
       <c r="D189" s="5">
         <v>4</v>
       </c>
-      <c r="E189" s="70"/>
+      <c r="E189" s="71"/>
       <c r="F189" s="5" t="s">
         <v>226</v>
       </c>
@@ -5126,15 +5132,15 @@
       <c r="H189" s="11"/>
     </row>
     <row r="190" spans="1:8">
-      <c r="A190" s="76"/>
+      <c r="A190" s="77"/>
       <c r="B190" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="C190" s="70"/>
+      <c r="C190" s="71"/>
       <c r="D190" s="5">
         <v>4</v>
       </c>
-      <c r="E190" s="70"/>
+      <c r="E190" s="71"/>
       <c r="F190" s="5" t="s">
         <v>226</v>
       </c>
@@ -5142,15 +5148,15 @@
       <c r="H190" s="11"/>
     </row>
     <row r="191" spans="1:8">
-      <c r="A191" s="76"/>
+      <c r="A191" s="77"/>
       <c r="B191" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="C191" s="70"/>
+      <c r="C191" s="71"/>
       <c r="D191" s="5">
         <v>4</v>
       </c>
-      <c r="E191" s="70"/>
+      <c r="E191" s="71"/>
       <c r="F191" s="5" t="s">
         <v>226</v>
       </c>
@@ -5158,15 +5164,15 @@
       <c r="H191" s="11"/>
     </row>
     <row r="192" spans="1:8">
-      <c r="A192" s="76"/>
+      <c r="A192" s="77"/>
       <c r="B192" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="C192" s="71"/>
+      <c r="C192" s="72"/>
       <c r="D192" s="67">
         <v>4</v>
       </c>
-      <c r="E192" s="71"/>
+      <c r="E192" s="72"/>
       <c r="F192" s="5" t="s">
         <v>226</v>
       </c>
@@ -5174,19 +5180,19 @@
       <c r="H192" s="11"/>
     </row>
     <row r="193" spans="1:8">
-      <c r="A193" s="76" t="s">
+      <c r="A193" s="77" t="s">
         <v>199</v>
       </c>
       <c r="B193" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="C193" s="69">
+      <c r="C193" s="70">
         <v>4</v>
       </c>
       <c r="D193" s="5">
         <v>4</v>
       </c>
-      <c r="E193" s="69" t="s">
+      <c r="E193" s="70" t="s">
         <v>252</v>
       </c>
       <c r="F193" s="5" t="s">
@@ -5196,15 +5202,15 @@
       <c r="H193" s="11"/>
     </row>
     <row r="194" spans="1:8">
-      <c r="A194" s="76"/>
+      <c r="A194" s="77"/>
       <c r="B194" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="C194" s="70"/>
+      <c r="C194" s="71"/>
       <c r="D194" s="5">
         <v>4</v>
       </c>
-      <c r="E194" s="70"/>
+      <c r="E194" s="71"/>
       <c r="F194" s="5" t="s">
         <v>252</v>
       </c>
@@ -5212,15 +5218,15 @@
       <c r="H194" s="11"/>
     </row>
     <row r="195" spans="1:8">
-      <c r="A195" s="76"/>
+      <c r="A195" s="77"/>
       <c r="B195" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="C195" s="70"/>
+      <c r="C195" s="71"/>
       <c r="D195" s="5">
         <v>4</v>
       </c>
-      <c r="E195" s="70"/>
+      <c r="E195" s="71"/>
       <c r="F195" s="5" t="s">
         <v>252</v>
       </c>
@@ -5228,15 +5234,15 @@
       <c r="H195" s="11"/>
     </row>
     <row r="196" spans="1:8">
-      <c r="A196" s="76"/>
+      <c r="A196" s="77"/>
       <c r="B196" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="C196" s="70"/>
+      <c r="C196" s="71"/>
       <c r="D196" s="5">
         <v>4</v>
       </c>
-      <c r="E196" s="70"/>
+      <c r="E196" s="71"/>
       <c r="F196" s="5" t="s">
         <v>252</v>
       </c>
@@ -5244,15 +5250,15 @@
       <c r="H196" s="11"/>
     </row>
     <row r="197" spans="1:8">
-      <c r="A197" s="76"/>
+      <c r="A197" s="77"/>
       <c r="B197" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="C197" s="70"/>
+      <c r="C197" s="71"/>
       <c r="D197" s="5">
         <v>4</v>
       </c>
-      <c r="E197" s="70"/>
+      <c r="E197" s="71"/>
       <c r="F197" s="5" t="s">
         <v>252</v>
       </c>
@@ -5260,15 +5266,15 @@
       <c r="H197" s="11"/>
     </row>
     <row r="198" spans="1:8">
-      <c r="A198" s="76"/>
+      <c r="A198" s="77"/>
       <c r="B198" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="C198" s="70"/>
+      <c r="C198" s="71"/>
       <c r="D198" s="5">
         <v>4</v>
       </c>
-      <c r="E198" s="70"/>
+      <c r="E198" s="71"/>
       <c r="F198" s="5" t="s">
         <v>252</v>
       </c>
@@ -5276,15 +5282,15 @@
       <c r="H198" s="11"/>
     </row>
     <row r="199" spans="1:8">
-      <c r="A199" s="76"/>
+      <c r="A199" s="77"/>
       <c r="B199" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="C199" s="70"/>
+      <c r="C199" s="71"/>
       <c r="D199" s="5">
         <v>4</v>
       </c>
-      <c r="E199" s="70"/>
+      <c r="E199" s="71"/>
       <c r="F199" s="5" t="s">
         <v>252</v>
       </c>
@@ -5292,15 +5298,15 @@
       <c r="H199" s="11"/>
     </row>
     <row r="200" spans="1:8">
-      <c r="A200" s="76"/>
+      <c r="A200" s="77"/>
       <c r="B200" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="C200" s="70"/>
+      <c r="C200" s="71"/>
       <c r="D200" s="5">
         <v>4</v>
       </c>
-      <c r="E200" s="70"/>
+      <c r="E200" s="71"/>
       <c r="F200" s="5" t="s">
         <v>252</v>
       </c>
@@ -5308,15 +5314,15 @@
       <c r="H200" s="11"/>
     </row>
     <row r="201" spans="1:8">
-      <c r="A201" s="76"/>
+      <c r="A201" s="77"/>
       <c r="B201" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="C201" s="71"/>
+      <c r="C201" s="72"/>
       <c r="D201" s="5">
         <v>4</v>
       </c>
-      <c r="E201" s="71"/>
+      <c r="E201" s="72"/>
       <c r="F201" s="5" t="s">
         <v>252</v>
       </c>
@@ -5324,19 +5330,19 @@
       <c r="H201" s="11"/>
     </row>
     <row r="202" spans="1:8">
-      <c r="A202" s="76" t="s">
+      <c r="A202" s="77" t="s">
         <v>209</v>
       </c>
       <c r="B202" s="7" t="s">
         <v>210</v>
       </c>
-      <c r="C202" s="69">
+      <c r="C202" s="70">
         <v>4</v>
       </c>
       <c r="D202" s="5">
         <v>4</v>
       </c>
-      <c r="E202" s="69" t="s">
+      <c r="E202" s="70" t="s">
         <v>226</v>
       </c>
       <c r="F202" s="5" t="s">
@@ -5346,15 +5352,15 @@
       <c r="H202" s="11"/>
     </row>
     <row r="203" spans="1:8">
-      <c r="A203" s="76"/>
+      <c r="A203" s="77"/>
       <c r="B203" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="C203" s="70"/>
+      <c r="C203" s="71"/>
       <c r="D203" s="5">
         <v>4</v>
       </c>
-      <c r="E203" s="70"/>
+      <c r="E203" s="71"/>
       <c r="F203" s="5" t="s">
         <v>226</v>
       </c>
@@ -5362,15 +5368,15 @@
       <c r="H203" s="11"/>
     </row>
     <row r="204" spans="1:8">
-      <c r="A204" s="76"/>
+      <c r="A204" s="77"/>
       <c r="B204" s="7" t="s">
         <v>212</v>
       </c>
-      <c r="C204" s="70"/>
+      <c r="C204" s="71"/>
       <c r="D204" s="5">
         <v>4</v>
       </c>
-      <c r="E204" s="70"/>
+      <c r="E204" s="71"/>
       <c r="F204" s="5" t="s">
         <v>226</v>
       </c>
@@ -5378,15 +5384,15 @@
       <c r="H204" s="11"/>
     </row>
     <row r="205" spans="1:8">
-      <c r="A205" s="76"/>
+      <c r="A205" s="77"/>
       <c r="B205" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="C205" s="70"/>
+      <c r="C205" s="71"/>
       <c r="D205" s="5">
         <v>4</v>
       </c>
-      <c r="E205" s="70"/>
+      <c r="E205" s="71"/>
       <c r="F205" s="5" t="s">
         <v>226</v>
       </c>
@@ -5394,15 +5400,15 @@
       <c r="H205" s="11"/>
     </row>
     <row r="206" spans="1:8">
-      <c r="A206" s="76"/>
+      <c r="A206" s="77"/>
       <c r="B206" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="C206" s="70"/>
+      <c r="C206" s="71"/>
       <c r="D206" s="5">
         <v>4</v>
       </c>
-      <c r="E206" s="70"/>
+      <c r="E206" s="71"/>
       <c r="F206" s="5" t="s">
         <v>226</v>
       </c>
@@ -5410,15 +5416,15 @@
       <c r="H206" s="11"/>
     </row>
     <row r="207" spans="1:8">
-      <c r="A207" s="76"/>
+      <c r="A207" s="77"/>
       <c r="B207" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="C207" s="70"/>
+      <c r="C207" s="71"/>
       <c r="D207" s="5">
         <v>4</v>
       </c>
-      <c r="E207" s="70"/>
+      <c r="E207" s="71"/>
       <c r="F207" s="5" t="s">
         <v>226</v>
       </c>
@@ -5426,15 +5432,15 @@
       <c r="H207" s="11"/>
     </row>
     <row r="208" spans="1:8">
-      <c r="A208" s="76"/>
+      <c r="A208" s="77"/>
       <c r="B208" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="C208" s="70"/>
+      <c r="C208" s="71"/>
       <c r="D208" s="5">
         <v>4</v>
       </c>
-      <c r="E208" s="70"/>
+      <c r="E208" s="71"/>
       <c r="F208" s="5" t="s">
         <v>226</v>
       </c>
@@ -5442,15 +5448,15 @@
       <c r="H208" s="11"/>
     </row>
     <row r="209" spans="1:8">
-      <c r="A209" s="76"/>
+      <c r="A209" s="77"/>
       <c r="B209" s="7" t="s">
         <v>216</v>
       </c>
-      <c r="C209" s="70"/>
+      <c r="C209" s="71"/>
       <c r="D209" s="5">
         <v>4</v>
       </c>
-      <c r="E209" s="70"/>
+      <c r="E209" s="71"/>
       <c r="F209" s="5" t="s">
         <v>226</v>
       </c>
@@ -5458,15 +5464,15 @@
       <c r="H209" s="11"/>
     </row>
     <row r="210" spans="1:8">
-      <c r="A210" s="76"/>
+      <c r="A210" s="77"/>
       <c r="B210" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="C210" s="70"/>
+      <c r="C210" s="71"/>
       <c r="D210" s="5">
         <v>4</v>
       </c>
-      <c r="E210" s="70"/>
+      <c r="E210" s="71"/>
       <c r="F210" s="5" t="s">
         <v>226</v>
       </c>
@@ -5474,15 +5480,15 @@
       <c r="H210" s="11"/>
     </row>
     <row r="211" spans="1:8">
-      <c r="A211" s="76"/>
+      <c r="A211" s="77"/>
       <c r="B211" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="C211" s="70"/>
+      <c r="C211" s="71"/>
       <c r="D211" s="5">
         <v>4</v>
       </c>
-      <c r="E211" s="70"/>
+      <c r="E211" s="71"/>
       <c r="F211" s="5" t="s">
         <v>226</v>
       </c>
@@ -5490,15 +5496,15 @@
       <c r="H211" s="11"/>
     </row>
     <row r="212" spans="1:8">
-      <c r="A212" s="77"/>
+      <c r="A212" s="78"/>
       <c r="B212" s="17" t="s">
         <v>219</v>
       </c>
-      <c r="C212" s="70"/>
+      <c r="C212" s="71"/>
       <c r="D212" s="16">
         <v>4</v>
       </c>
-      <c r="E212" s="70"/>
+      <c r="E212" s="71"/>
       <c r="F212" s="16" t="s">
         <v>226</v>
       </c>
@@ -5528,19 +5534,19 @@
       <c r="H213" s="22"/>
     </row>
     <row r="214" spans="1:8">
-      <c r="A214" s="89" t="s">
+      <c r="A214" s="98" t="s">
         <v>230</v>
       </c>
       <c r="B214" s="20" t="s">
         <v>264</v>
       </c>
-      <c r="C214" s="91">
+      <c r="C214" s="95">
         <v>3</v>
       </c>
       <c r="D214" s="44">
         <v>0</v>
       </c>
-      <c r="E214" s="91" t="s">
+      <c r="E214" s="95" t="s">
         <v>252</v>
       </c>
       <c r="F214" s="44" t="s">
@@ -5550,31 +5556,31 @@
       <c r="H214" s="20"/>
     </row>
     <row r="215" spans="1:8">
-      <c r="A215" s="97"/>
+      <c r="A215" s="99"/>
       <c r="B215" s="20" t="s">
         <v>231</v>
       </c>
-      <c r="C215" s="98"/>
+      <c r="C215" s="96"/>
       <c r="D215" s="56">
         <v>3</v>
       </c>
-      <c r="E215" s="98"/>
+      <c r="E215" s="96"/>
       <c r="F215" s="56" t="s">
         <v>226</v>
       </c>
       <c r="G215" s="56"/>
-      <c r="H215" s="99"/>
+      <c r="H215" s="69"/>
     </row>
     <row r="216" spans="1:8">
-      <c r="A216" s="90"/>
+      <c r="A216" s="100"/>
       <c r="B216" s="20" t="s">
         <v>256</v>
       </c>
-      <c r="C216" s="92"/>
+      <c r="C216" s="97"/>
       <c r="D216" s="21">
         <v>3</v>
       </c>
-      <c r="E216" s="92"/>
+      <c r="E216" s="97"/>
       <c r="F216" s="21" t="s">
         <v>226</v>
       </c>
@@ -5582,19 +5588,19 @@
       <c r="H216" s="20"/>
     </row>
     <row r="217" spans="1:8">
-      <c r="A217" s="93" t="s">
+      <c r="A217" s="101" t="s">
         <v>232</v>
       </c>
       <c r="B217" s="20" t="s">
         <v>233</v>
       </c>
-      <c r="C217" s="94">
+      <c r="C217" s="102">
         <v>4</v>
       </c>
       <c r="D217" s="65">
         <v>4</v>
       </c>
-      <c r="E217" s="94" t="s">
+      <c r="E217" s="102" t="s">
         <v>252</v>
       </c>
       <c r="F217" s="21" t="s">
@@ -5604,15 +5610,15 @@
       <c r="H217" s="22"/>
     </row>
     <row r="218" spans="1:8">
-      <c r="A218" s="93"/>
+      <c r="A218" s="101"/>
       <c r="B218" s="47" t="s">
         <v>234</v>
       </c>
-      <c r="C218" s="91"/>
+      <c r="C218" s="95"/>
       <c r="D218" s="60">
         <v>4</v>
       </c>
-      <c r="E218" s="91"/>
+      <c r="E218" s="95"/>
       <c r="F218" s="61" t="s">
         <v>226</v>
       </c>
@@ -5620,15 +5626,15 @@
       <c r="H218" s="49"/>
     </row>
     <row r="219" spans="1:8">
-      <c r="A219" s="93"/>
+      <c r="A219" s="101"/>
       <c r="B219" s="47" t="s">
         <v>260</v>
       </c>
-      <c r="C219" s="91"/>
+      <c r="C219" s="95"/>
       <c r="D219" s="60">
         <v>4</v>
       </c>
-      <c r="E219" s="91"/>
+      <c r="E219" s="95"/>
       <c r="F219" s="61" t="s">
         <v>252</v>
       </c>
@@ -5636,15 +5642,15 @@
       <c r="H219" s="49"/>
     </row>
     <row r="220" spans="1:8">
-      <c r="A220" s="93"/>
+      <c r="A220" s="101"/>
       <c r="B220" s="47" t="s">
         <v>261</v>
       </c>
-      <c r="C220" s="91"/>
+      <c r="C220" s="95"/>
       <c r="D220" s="60">
         <v>4</v>
       </c>
-      <c r="E220" s="91"/>
+      <c r="E220" s="95"/>
       <c r="F220" s="48" t="s">
         <v>252</v>
       </c>
@@ -5652,19 +5658,19 @@
       <c r="H220" s="49"/>
     </row>
     <row r="221" spans="1:8">
-      <c r="A221" s="100" t="s">
+      <c r="A221" s="92" t="s">
         <v>254</v>
       </c>
       <c r="B221" s="50" t="s">
         <v>255</v>
       </c>
-      <c r="C221" s="91">
+      <c r="C221" s="95">
         <v>4</v>
       </c>
       <c r="D221" s="60">
         <v>4</v>
       </c>
-      <c r="E221" s="91" t="s">
+      <c r="E221" s="95" t="s">
         <v>252</v>
       </c>
       <c r="F221" s="46" t="s">
@@ -5674,22 +5680,34 @@
       <c r="H221" s="51"/>
     </row>
     <row r="222" spans="1:8">
-      <c r="A222" s="101"/>
-      <c r="B222" s="50"/>
-      <c r="C222" s="98"/>
-      <c r="D222" s="66"/>
-      <c r="E222" s="98"/>
-      <c r="F222" s="66"/>
+      <c r="A222" s="93"/>
+      <c r="B222" s="50" t="s">
+        <v>265</v>
+      </c>
+      <c r="C222" s="96"/>
+      <c r="D222" s="66">
+        <v>4</v>
+      </c>
+      <c r="E222" s="96"/>
+      <c r="F222" s="66" t="s">
+        <v>252</v>
+      </c>
       <c r="G222" s="51"/>
       <c r="H222" s="51"/>
     </row>
     <row r="223" spans="1:8">
-      <c r="A223" s="102"/>
-      <c r="B223" s="50"/>
-      <c r="C223" s="92"/>
-      <c r="D223" s="66"/>
-      <c r="E223" s="92"/>
-      <c r="F223" s="66"/>
+      <c r="A223" s="94"/>
+      <c r="B223" s="50" t="s">
+        <v>266</v>
+      </c>
+      <c r="C223" s="97"/>
+      <c r="D223" s="66">
+        <v>4</v>
+      </c>
+      <c r="E223" s="97"/>
+      <c r="F223" s="66" t="s">
+        <v>252</v>
+      </c>
       <c r="G223" s="51"/>
       <c r="H223" s="51"/>
     </row>
@@ -5792,7 +5810,6 @@
     <mergeCell ref="E82:E90"/>
     <mergeCell ref="C70:C81"/>
     <mergeCell ref="E70:E81"/>
-    <mergeCell ref="C147:C153"/>
     <mergeCell ref="C105:C110"/>
     <mergeCell ref="E105:E110"/>
     <mergeCell ref="C100:C104"/>
@@ -5803,8 +5820,6 @@
     <mergeCell ref="E116:E122"/>
     <mergeCell ref="C111:C115"/>
     <mergeCell ref="E111:E115"/>
-    <mergeCell ref="E123:E130"/>
-    <mergeCell ref="C154:C159"/>
     <mergeCell ref="E147:E153"/>
     <mergeCell ref="E154:E159"/>
     <mergeCell ref="C160:C163"/>
@@ -5813,6 +5828,8 @@
     <mergeCell ref="E164:E169"/>
     <mergeCell ref="C170:C171"/>
     <mergeCell ref="E170:E171"/>
+    <mergeCell ref="C147:C153"/>
+    <mergeCell ref="E123:E130"/>
     <mergeCell ref="C174:C181"/>
     <mergeCell ref="E174:E181"/>
     <mergeCell ref="C187:C192"/>
@@ -5821,6 +5838,7 @@
     <mergeCell ref="E193:E201"/>
     <mergeCell ref="C202:C212"/>
     <mergeCell ref="E202:E212"/>
+    <mergeCell ref="C154:C159"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
